--- a/research/traditional_assets/database/data/mexico/mexico_retail_rei_ts.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_retail_rei_ts.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08697120886928461</v>
+        <v>0.08674179524267676</v>
       </c>
       <c r="C2">
-        <v>839.2583465859491</v>
+        <v>832.7650278012522</v>
       </c>
       <c r="D2">
-        <v>808.558346585949</v>
+        <v>811.2100278012522</v>
       </c>
       <c r="E2">
-        <v>-628.7</v>
+        <v>-619.5550000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.145</v>
       </c>
       <c r="G2">
         <v>30.7</v>
@@ -1451,28 +1451,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4599934999999999</v>
       </c>
       <c r="N2">
-        <v>142.9333333333333</v>
+        <v>142.4733398333333</v>
       </c>
       <c r="O2">
-        <v>42.88</v>
+        <v>42.74200195</v>
       </c>
       <c r="P2">
-        <v>100.0533333333333</v>
+        <v>99.73133788333334</v>
       </c>
       <c r="Q2">
-        <v>100.9533333333333</v>
+        <v>100.6313378833333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08697120886928461</v>
+        <v>0.08726231842694623</v>
       </c>
       <c r="T2">
-        <v>0.5990912546403601</v>
+        <v>0.6033272534105444</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>310.7290284174306</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08674179524267676</v>
+        <v>0.0865123816160689</v>
       </c>
       <c r="C3">
-        <v>832.7650278012522</v>
+        <v>826.2891587128287</v>
       </c>
       <c r="D3">
-        <v>811.2100278012522</v>
+        <v>813.8791587128286</v>
       </c>
       <c r="E3">
-        <v>-619.5550000000001</v>
+        <v>-610.4100000000001</v>
       </c>
       <c r="F3">
-        <v>9.145</v>
+        <v>18.29</v>
       </c>
       <c r="G3">
         <v>30.7</v>
@@ -1533,28 +1533,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M3">
-        <v>0.4599934999999999</v>
+        <v>0.9199869999999999</v>
       </c>
       <c r="N3">
-        <v>142.4733398333333</v>
+        <v>142.0133463333333</v>
       </c>
       <c r="O3">
-        <v>42.74200195</v>
+        <v>42.6040039</v>
       </c>
       <c r="P3">
-        <v>99.73133788333334</v>
+        <v>99.40934243333334</v>
       </c>
       <c r="Q3">
-        <v>100.6313378833333</v>
+        <v>100.3093424333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08726231842694623</v>
+        <v>0.08755936899598868</v>
       </c>
       <c r="T3">
-        <v>0.6033272534105444</v>
+        <v>0.6076497011352223</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>310.7290284174306</v>
+        <v>155.3645142087153</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0865123816160689</v>
+        <v>0.08628296798946104</v>
       </c>
       <c r="C4">
-        <v>826.2891587128287</v>
+        <v>819.8309121339171</v>
       </c>
       <c r="D4">
-        <v>813.8791587128286</v>
+        <v>816.565912133917</v>
       </c>
       <c r="E4">
-        <v>-610.4100000000001</v>
+        <v>-601.2650000000001</v>
       </c>
       <c r="F4">
-        <v>18.29</v>
+        <v>27.435</v>
       </c>
       <c r="G4">
         <v>30.7</v>
@@ -1615,28 +1615,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M4">
-        <v>0.9199869999999999</v>
+        <v>1.3799805</v>
       </c>
       <c r="N4">
-        <v>142.0133463333333</v>
+        <v>141.5533528333333</v>
       </c>
       <c r="O4">
-        <v>42.6040039</v>
+        <v>42.46600585</v>
       </c>
       <c r="P4">
-        <v>99.40934243333334</v>
+        <v>99.08734698333335</v>
       </c>
       <c r="Q4">
-        <v>100.3093424333333</v>
+        <v>99.98734698333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08755936899598868</v>
+        <v>0.08786254431903201</v>
       </c>
       <c r="T4">
-        <v>0.6076497011352223</v>
+        <v>0.6120612714933987</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>155.3645142087153</v>
+        <v>103.5763428058102</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08628296798946104</v>
+        <v>0.08605355436285321</v>
       </c>
       <c r="C5">
-        <v>819.8309121339171</v>
+        <v>813.3904631672575</v>
       </c>
       <c r="D5">
-        <v>816.565912133917</v>
+        <v>819.2704631672575</v>
       </c>
       <c r="E5">
-        <v>-601.2650000000001</v>
+        <v>-592.12</v>
       </c>
       <c r="F5">
-        <v>27.435</v>
+        <v>36.58</v>
       </c>
       <c r="G5">
         <v>30.7</v>
@@ -1697,28 +1697,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M5">
-        <v>1.3799805</v>
+        <v>1.839974</v>
       </c>
       <c r="N5">
-        <v>141.5533528333333</v>
+        <v>141.0933593333333</v>
       </c>
       <c r="O5">
-        <v>42.46600585</v>
+        <v>42.32800779999999</v>
       </c>
       <c r="P5">
-        <v>99.08734698333335</v>
+        <v>98.76535153333333</v>
       </c>
       <c r="Q5">
-        <v>99.98734698333334</v>
+        <v>99.66535153333332</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08786254431903201</v>
+        <v>0.08817203579463875</v>
       </c>
       <c r="T5">
-        <v>0.6120612714933987</v>
+        <v>0.6165647495673705</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>103.5763428058102</v>
+        <v>77.68225710435763</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08605355436285321</v>
+        <v>0.08582414073624535</v>
       </c>
       <c r="C6">
-        <v>813.3904631672575</v>
+        <v>806.9679892431338</v>
       </c>
       <c r="D6">
-        <v>819.2704631672575</v>
+        <v>821.9929892431338</v>
       </c>
       <c r="E6">
-        <v>-592.12</v>
+        <v>-582.975</v>
       </c>
       <c r="F6">
-        <v>36.58</v>
+        <v>45.725</v>
       </c>
       <c r="G6">
         <v>30.7</v>
@@ -1779,28 +1779,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M6">
-        <v>1.839974</v>
+        <v>2.2999675</v>
       </c>
       <c r="N6">
-        <v>141.0933593333333</v>
+        <v>140.6333658333333</v>
       </c>
       <c r="O6">
-        <v>42.32800779999999</v>
+        <v>42.19000974999999</v>
       </c>
       <c r="P6">
-        <v>98.76535153333333</v>
+        <v>98.44335608333333</v>
       </c>
       <c r="Q6">
-        <v>99.66535153333332</v>
+        <v>99.34335608333332</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08817203579463875</v>
+        <v>0.08848804288025827</v>
       </c>
       <c r="T6">
-        <v>0.6165647495673705</v>
+        <v>0.6211630377060575</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>77.68225710435763</v>
+        <v>62.1458056834861</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08582414073624535</v>
+        <v>0.08559472710963749</v>
       </c>
       <c r="C7">
-        <v>806.9679892431338</v>
+        <v>800.5636701581744</v>
       </c>
       <c r="D7">
-        <v>821.9929892431338</v>
+        <v>824.7336701581744</v>
       </c>
       <c r="E7">
-        <v>-582.975</v>
+        <v>-573.83</v>
       </c>
       <c r="F7">
-        <v>45.725</v>
+        <v>54.87</v>
       </c>
       <c r="G7">
         <v>30.7</v>
@@ -1861,28 +1861,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M7">
-        <v>2.2999675</v>
+        <v>2.759961</v>
       </c>
       <c r="N7">
-        <v>140.6333658333333</v>
+        <v>140.1733723333333</v>
       </c>
       <c r="O7">
-        <v>42.19000974999999</v>
+        <v>42.0520117</v>
       </c>
       <c r="P7">
-        <v>98.44335608333333</v>
+        <v>98.12136063333332</v>
       </c>
       <c r="Q7">
-        <v>99.34335608333332</v>
+        <v>99.02136063333332</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08848804288025827</v>
+        <v>0.08881077352089095</v>
       </c>
       <c r="T7">
-        <v>0.6211630377060575</v>
+        <v>0.6258591617625888</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>62.1458056834861</v>
+        <v>51.78817140290509</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08559472710963749</v>
+        <v>0.08536531348302966</v>
       </c>
       <c r="C8">
-        <v>800.5636701581744</v>
+        <v>794.1776881149335</v>
       </c>
       <c r="D8">
-        <v>824.7336701581744</v>
+        <v>827.4926881149335</v>
       </c>
       <c r="E8">
-        <v>-573.83</v>
+        <v>-564.6850000000001</v>
       </c>
       <c r="F8">
-        <v>54.87</v>
+        <v>64.01499999999999</v>
       </c>
       <c r="G8">
         <v>30.7</v>
@@ -1943,28 +1943,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M8">
-        <v>2.759961</v>
+        <v>3.219954499999999</v>
       </c>
       <c r="N8">
-        <v>140.1733723333333</v>
+        <v>139.7133788333333</v>
       </c>
       <c r="O8">
-        <v>42.0520117</v>
+        <v>41.91401365</v>
       </c>
       <c r="P8">
-        <v>98.12136063333332</v>
+        <v>97.79936518333334</v>
       </c>
       <c r="Q8">
-        <v>99.02136063333332</v>
+        <v>98.69936518333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08881077352089095</v>
+        <v>0.08914044460540822</v>
       </c>
       <c r="T8">
-        <v>0.6258591617625888</v>
+        <v>0.6306562777343145</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>51.78817140290509</v>
+        <v>44.38986120249009</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08536531348302964</v>
+        <v>0.0851358998564218</v>
       </c>
       <c r="C9">
-        <v>794.1776881149336</v>
+        <v>787.8102277622713</v>
       </c>
       <c r="D9">
-        <v>827.4926881149336</v>
+        <v>830.2702277622712</v>
       </c>
       <c r="E9">
-        <v>-564.6850000000001</v>
+        <v>-555.5400000000001</v>
       </c>
       <c r="F9">
-        <v>64.015</v>
+        <v>73.16</v>
       </c>
       <c r="G9">
         <v>30.7</v>
@@ -2025,28 +2025,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M9">
-        <v>3.2199545</v>
+        <v>3.679948</v>
       </c>
       <c r="N9">
-        <v>139.7133788333333</v>
+        <v>139.2533853333333</v>
       </c>
       <c r="O9">
-        <v>41.91401365</v>
+        <v>41.7760156</v>
       </c>
       <c r="P9">
-        <v>97.79936518333334</v>
+        <v>97.47736973333335</v>
       </c>
       <c r="Q9">
-        <v>98.69936518333333</v>
+        <v>98.37736973333334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08914044460540822</v>
+        <v>0.0894772824526324</v>
       </c>
       <c r="T9">
-        <v>0.6306562777343145</v>
+        <v>0.6355576788358603</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.38986120249007</v>
+        <v>38.84112855217882</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0851358998564218</v>
+        <v>0.08490648622981394</v>
       </c>
       <c r="C10">
-        <v>787.8102277622713</v>
+        <v>781.4614762365463</v>
       </c>
       <c r="D10">
-        <v>830.2702277622712</v>
+        <v>833.0664762365462</v>
       </c>
       <c r="E10">
-        <v>-555.5400000000001</v>
+        <v>-546.3950000000001</v>
       </c>
       <c r="F10">
-        <v>73.16</v>
+        <v>82.30499999999999</v>
       </c>
       <c r="G10">
         <v>30.7</v>
@@ -2107,28 +2107,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M10">
-        <v>3.679948</v>
+        <v>4.139941499999999</v>
       </c>
       <c r="N10">
-        <v>139.2533853333333</v>
+        <v>138.7933918333333</v>
       </c>
       <c r="O10">
-        <v>41.7760156</v>
+        <v>41.63801755</v>
       </c>
       <c r="P10">
-        <v>97.47736973333335</v>
+        <v>97.15537428333334</v>
       </c>
       <c r="Q10">
-        <v>98.37736973333334</v>
+        <v>98.05537428333334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0894772824526324</v>
+        <v>0.08982152332946586</v>
       </c>
       <c r="T10">
-        <v>0.6355576788358603</v>
+        <v>0.6405668030385389</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.84112855217882</v>
+        <v>34.52544760193674</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08490648622981394</v>
+        <v>0.08467707260320607</v>
       </c>
       <c r="C11">
-        <v>781.4614762365463</v>
+        <v>775.1316232036456</v>
       </c>
       <c r="D11">
-        <v>833.0664762365462</v>
+        <v>835.8816232036455</v>
       </c>
       <c r="E11">
-        <v>-546.3950000000001</v>
+        <v>-537.25</v>
       </c>
       <c r="F11">
-        <v>82.30499999999999</v>
+        <v>91.44999999999999</v>
       </c>
       <c r="G11">
         <v>30.7</v>
@@ -2189,28 +2189,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M11">
-        <v>4.139941499999999</v>
+        <v>4.599934999999999</v>
       </c>
       <c r="N11">
-        <v>138.7933918333333</v>
+        <v>138.3333983333333</v>
       </c>
       <c r="O11">
-        <v>41.63801755</v>
+        <v>41.5000195</v>
       </c>
       <c r="P11">
-        <v>97.15537428333334</v>
+        <v>96.83337883333334</v>
       </c>
       <c r="Q11">
-        <v>98.05537428333334</v>
+        <v>97.73337883333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08982152332946586</v>
+        <v>0.09017341400356231</v>
       </c>
       <c r="T11">
-        <v>0.6405668030385389</v>
+        <v>0.6456872411123881</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.52544760193674</v>
+        <v>31.07290284174306</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08467707260320607</v>
+        <v>0.08444765897659824</v>
       </c>
       <c r="C12">
-        <v>775.1316232036455</v>
+        <v>768.8208609018686</v>
       </c>
       <c r="D12">
-        <v>835.8816232036455</v>
+        <v>838.7158609018686</v>
       </c>
       <c r="E12">
-        <v>-537.25</v>
+        <v>-528.105</v>
       </c>
       <c r="F12">
-        <v>91.45</v>
+        <v>100.595</v>
       </c>
       <c r="G12">
         <v>30.7</v>
@@ -2271,28 +2271,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M12">
-        <v>4.599935</v>
+        <v>5.0599285</v>
       </c>
       <c r="N12">
-        <v>138.3333983333333</v>
+        <v>137.8734048333333</v>
       </c>
       <c r="O12">
-        <v>41.5000195</v>
+        <v>41.36202144999999</v>
       </c>
       <c r="P12">
-        <v>96.83337883333334</v>
+        <v>96.51138338333334</v>
       </c>
       <c r="Q12">
-        <v>97.73337883333333</v>
+        <v>97.41138338333333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09017341400356231</v>
+        <v>0.09053321233325644</v>
       </c>
       <c r="T12">
-        <v>0.6456872411123881</v>
+        <v>0.6509227452103687</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.07290284174305</v>
+        <v>28.24809349249368</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08444765897659824</v>
+        <v>0.08421824534999038</v>
       </c>
       <c r="C13">
-        <v>768.8208609018686</v>
+        <v>762.5293841856899</v>
       </c>
       <c r="D13">
-        <v>838.7158609018686</v>
+        <v>841.5693841856898</v>
       </c>
       <c r="E13">
-        <v>-528.105</v>
+        <v>-518.96</v>
       </c>
       <c r="F13">
-        <v>100.595</v>
+        <v>109.74</v>
       </c>
       <c r="G13">
         <v>30.7</v>
@@ -2353,28 +2353,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M13">
-        <v>5.0599285</v>
+        <v>5.519921999999999</v>
       </c>
       <c r="N13">
-        <v>137.8734048333333</v>
+        <v>137.4134113333333</v>
       </c>
       <c r="O13">
-        <v>41.36202144999999</v>
+        <v>41.2240234</v>
       </c>
       <c r="P13">
-        <v>96.51138338333334</v>
+        <v>96.18938793333334</v>
       </c>
       <c r="Q13">
-        <v>97.41138338333333</v>
+        <v>97.08938793333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09053321233325644</v>
+        <v>0.09090118789771634</v>
       </c>
       <c r="T13">
-        <v>0.6509227452103687</v>
+        <v>0.656277238037849</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.24809349249368</v>
+        <v>25.89408570145255</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08421824534999038</v>
+        <v>0.08398883172338252</v>
       </c>
       <c r="C14">
-        <v>762.5293841856899</v>
+        <v>756.2573905704114</v>
       </c>
       <c r="D14">
-        <v>841.5693841856898</v>
+        <v>844.4423905704114</v>
       </c>
       <c r="E14">
-        <v>-518.96</v>
+        <v>-509.8150000000001</v>
       </c>
       <c r="F14">
-        <v>109.74</v>
+        <v>118.885</v>
       </c>
       <c r="G14">
         <v>30.7</v>
@@ -2435,28 +2435,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M14">
-        <v>5.519921999999999</v>
+        <v>5.9799155</v>
       </c>
       <c r="N14">
-        <v>137.4134113333333</v>
+        <v>136.9534178333333</v>
       </c>
       <c r="O14">
-        <v>41.2240234</v>
+        <v>41.08602535</v>
       </c>
       <c r="P14">
-        <v>96.18938793333334</v>
+        <v>95.86739248333333</v>
       </c>
       <c r="Q14">
-        <v>97.08938793333333</v>
+        <v>96.76739248333332</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09090118789771634</v>
+        <v>0.09127762267055461</v>
       </c>
       <c r="T14">
-        <v>0.656277238037849</v>
+        <v>0.6617548226544666</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.89408570145255</v>
+        <v>23.90223295518696</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08398883172338252</v>
+        <v>0.08375941809677466</v>
       </c>
       <c r="C15">
-        <v>756.2573905704114</v>
+        <v>750.0050802777396</v>
       </c>
       <c r="D15">
-        <v>844.4423905704114</v>
+        <v>847.3350802777395</v>
       </c>
       <c r="E15">
-        <v>-509.8150000000001</v>
+        <v>-500.6700000000001</v>
       </c>
       <c r="F15">
-        <v>118.885</v>
+        <v>128.03</v>
       </c>
       <c r="G15">
         <v>30.7</v>
@@ -2517,28 +2517,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M15">
-        <v>5.9799155</v>
+        <v>6.439909</v>
       </c>
       <c r="N15">
-        <v>136.9534178333333</v>
+        <v>136.4934243333333</v>
       </c>
       <c r="O15">
-        <v>41.08602535</v>
+        <v>40.9480273</v>
       </c>
       <c r="P15">
-        <v>95.86739248333333</v>
+        <v>95.54539703333333</v>
       </c>
       <c r="Q15">
-        <v>96.76739248333332</v>
+        <v>96.44539703333332</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09127762267055461</v>
+        <v>0.09166281174043565</v>
       </c>
       <c r="T15">
-        <v>0.6617548226544666</v>
+        <v>0.6673597929598429</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.90223295518696</v>
+        <v>22.19493060124504</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08375941809677466</v>
+        <v>0.08353000447016681</v>
       </c>
       <c r="C16">
-        <v>750.0050802777396</v>
+        <v>743.7726562822984</v>
       </c>
       <c r="D16">
-        <v>847.3350802777395</v>
+        <v>850.2476562822983</v>
       </c>
       <c r="E16">
-        <v>-500.6700000000001</v>
+        <v>-491.525</v>
       </c>
       <c r="F16">
-        <v>128.03</v>
+        <v>137.175</v>
       </c>
       <c r="G16">
         <v>30.7</v>
@@ -2599,28 +2599,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M16">
-        <v>6.439909</v>
+        <v>6.8999025</v>
       </c>
       <c r="N16">
-        <v>136.4934243333333</v>
+        <v>136.0334308333333</v>
       </c>
       <c r="O16">
-        <v>40.9480273</v>
+        <v>40.81002925</v>
       </c>
       <c r="P16">
-        <v>95.54539703333333</v>
+        <v>95.22340158333334</v>
       </c>
       <c r="Q16">
-        <v>96.44539703333332</v>
+        <v>96.12340158333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09166281174043565</v>
+        <v>0.0920570640825492</v>
       </c>
       <c r="T16">
-        <v>0.6673597929598429</v>
+        <v>0.6730966449194634</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.19493060124504</v>
+        <v>20.71526856116203</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08353000447016681</v>
+        <v>0.08330059084355895</v>
       </c>
       <c r="C17">
-        <v>743.7726562822984</v>
+        <v>737.5603243591063</v>
       </c>
       <c r="D17">
-        <v>850.2476562822983</v>
+        <v>853.1803243591063</v>
       </c>
       <c r="E17">
-        <v>-491.5250000000001</v>
+        <v>-482.3800000000001</v>
       </c>
       <c r="F17">
-        <v>137.175</v>
+        <v>146.32</v>
       </c>
       <c r="G17">
         <v>30.7</v>
@@ -2681,28 +2681,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M17">
-        <v>6.899902499999999</v>
+        <v>7.359895999999999</v>
       </c>
       <c r="N17">
-        <v>136.0334308333333</v>
+        <v>135.5734373333333</v>
       </c>
       <c r="O17">
-        <v>40.81002925</v>
+        <v>40.6720312</v>
       </c>
       <c r="P17">
-        <v>95.22340158333334</v>
+        <v>94.90140613333335</v>
       </c>
       <c r="Q17">
-        <v>96.12340158333333</v>
+        <v>95.80140613333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0920570640825492</v>
+        <v>0.09246070338518923</v>
       </c>
       <c r="T17">
-        <v>0.6730966449194634</v>
+        <v>0.678970088592408</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.71526856116204</v>
+        <v>19.42056427608941</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08330059084355895</v>
+        <v>0.08307117721695111</v>
       </c>
       <c r="C18">
-        <v>737.5603243591063</v>
+        <v>731.3682931320388</v>
       </c>
       <c r="D18">
-        <v>853.1803243591063</v>
+        <v>856.1332931320388</v>
       </c>
       <c r="E18">
-        <v>-482.3800000000001</v>
+        <v>-473.235</v>
       </c>
       <c r="F18">
-        <v>146.32</v>
+        <v>155.465</v>
       </c>
       <c r="G18">
         <v>30.7</v>
@@ -2763,28 +2763,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M18">
-        <v>7.359895999999999</v>
+        <v>7.819889499999999</v>
       </c>
       <c r="N18">
-        <v>135.5734373333333</v>
+        <v>135.1134438333333</v>
       </c>
       <c r="O18">
-        <v>40.6720312</v>
+        <v>40.53403315000001</v>
       </c>
       <c r="P18">
-        <v>94.90140613333335</v>
+        <v>94.57941068333335</v>
       </c>
       <c r="Q18">
-        <v>95.80140613333334</v>
+        <v>95.47941068333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09246070338518923</v>
+        <v>0.09287406893608567</v>
       </c>
       <c r="T18">
-        <v>0.678970088592408</v>
+        <v>0.6849850610285563</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.42056427608941</v>
+        <v>18.2781781422018</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08307117721695111</v>
+        <v>0.08284176359034325</v>
       </c>
       <c r="C19">
-        <v>731.3682931320388</v>
+        <v>725.1967741233015</v>
       </c>
       <c r="D19">
-        <v>856.1332931320388</v>
+        <v>859.1067741233014</v>
       </c>
       <c r="E19">
-        <v>-473.235</v>
+        <v>-464.09</v>
       </c>
       <c r="F19">
-        <v>155.465</v>
+        <v>164.61</v>
       </c>
       <c r="G19">
         <v>30.7</v>
@@ -2845,28 +2845,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M19">
-        <v>7.819889499999999</v>
+        <v>8.279883</v>
       </c>
       <c r="N19">
-        <v>135.1134438333333</v>
+        <v>134.6534503333333</v>
       </c>
       <c r="O19">
-        <v>40.53403315000001</v>
+        <v>40.3960351</v>
       </c>
       <c r="P19">
-        <v>94.57941068333335</v>
+        <v>94.25741523333332</v>
       </c>
       <c r="Q19">
-        <v>95.47941068333334</v>
+        <v>95.15741523333331</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09287406893608567</v>
+        <v>0.09329751657358933</v>
       </c>
       <c r="T19">
-        <v>0.6849850610285563</v>
+        <v>0.6911467401094885</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.2781781422018</v>
+        <v>17.26272380096836</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08284176359034326</v>
+        <v>0.0826123499637354</v>
       </c>
       <c r="C20">
-        <v>725.1967741233012</v>
+        <v>719.0459818039358</v>
       </c>
       <c r="D20">
-        <v>859.1067741233012</v>
+        <v>862.1009818039357</v>
       </c>
       <c r="E20">
-        <v>-464.09</v>
+        <v>-454.9450000000001</v>
       </c>
       <c r="F20">
-        <v>164.61</v>
+        <v>173.755</v>
       </c>
       <c r="G20">
         <v>30.7</v>
@@ -2927,28 +2927,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M20">
-        <v>8.279882999999998</v>
+        <v>8.739876499999999</v>
       </c>
       <c r="N20">
-        <v>134.6534503333334</v>
+        <v>134.1934568333333</v>
       </c>
       <c r="O20">
-        <v>40.39603510000001</v>
+        <v>40.25803705</v>
       </c>
       <c r="P20">
-        <v>94.25741523333335</v>
+        <v>93.93541978333333</v>
       </c>
       <c r="Q20">
-        <v>95.15741523333334</v>
+        <v>94.83541978333332</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09329751657358933</v>
+        <v>0.09373141970831531</v>
       </c>
       <c r="T20">
-        <v>0.6911467401094885</v>
+        <v>0.6974605594146414</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.26272380096837</v>
+        <v>16.35415939039108</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0826123499637354</v>
+        <v>0.08238293633712757</v>
       </c>
       <c r="C21">
-        <v>719.0459818039358</v>
+        <v>712.9161336453875</v>
       </c>
       <c r="D21">
-        <v>862.1009818039357</v>
+        <v>865.1161336453874</v>
       </c>
       <c r="E21">
-        <v>-454.9450000000001</v>
+        <v>-445.8000000000001</v>
       </c>
       <c r="F21">
-        <v>173.755</v>
+        <v>182.9</v>
       </c>
       <c r="G21">
         <v>30.7</v>
@@ -3009,28 +3009,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M21">
-        <v>8.739876499999999</v>
+        <v>9.199870000000001</v>
       </c>
       <c r="N21">
-        <v>134.1934568333333</v>
+        <v>133.7334633333333</v>
       </c>
       <c r="O21">
-        <v>40.25803705</v>
+        <v>40.120039</v>
       </c>
       <c r="P21">
-        <v>93.93541978333333</v>
+        <v>93.61342433333334</v>
       </c>
       <c r="Q21">
-        <v>94.83541978333332</v>
+        <v>94.51342433333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09373141970831531</v>
+        <v>0.09417617042140944</v>
       </c>
       <c r="T21">
-        <v>0.6974605594146414</v>
+        <v>0.7039322242024231</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.35415939039108</v>
+        <v>15.53645142087153</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08238293633712757</v>
+        <v>0.08215352271051969</v>
       </c>
       <c r="C22">
-        <v>712.9161336453875</v>
+        <v>706.8074501721599</v>
       </c>
       <c r="D22">
-        <v>865.1161336453874</v>
+        <v>868.1524501721598</v>
       </c>
       <c r="E22">
-        <v>-445.8000000000001</v>
+        <v>-436.655</v>
       </c>
       <c r="F22">
-        <v>182.9</v>
+        <v>192.045</v>
       </c>
       <c r="G22">
         <v>30.7</v>
@@ -3091,28 +3091,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M22">
-        <v>9.199870000000001</v>
+        <v>9.6598635</v>
       </c>
       <c r="N22">
-        <v>133.7334633333333</v>
+        <v>133.2734698333333</v>
       </c>
       <c r="O22">
-        <v>40.120039</v>
+        <v>39.98204095</v>
       </c>
       <c r="P22">
-        <v>93.61342433333334</v>
+        <v>93.29142888333334</v>
       </c>
       <c r="Q22">
-        <v>94.51342433333333</v>
+        <v>94.19142888333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09417617042140944</v>
+        <v>0.09463218064622746</v>
       </c>
       <c r="T22">
-        <v>0.7039322242024231</v>
+        <v>0.7105677286050853</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.53645142087153</v>
+        <v>14.79662040083003</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08215352271051968</v>
+        <v>0.08192410908391183</v>
       </c>
       <c r="C23">
-        <v>706.8074501721601</v>
+        <v>700.7201550155767</v>
       </c>
       <c r="D23">
-        <v>868.15245017216</v>
+        <v>871.2101550155766</v>
       </c>
       <c r="E23">
-        <v>-436.6550000000001</v>
+        <v>-427.51</v>
       </c>
       <c r="F23">
-        <v>192.045</v>
+        <v>201.19</v>
       </c>
       <c r="G23">
         <v>30.7</v>
@@ -3173,28 +3173,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M23">
-        <v>9.659863499999998</v>
+        <v>10.119857</v>
       </c>
       <c r="N23">
-        <v>133.2734698333333</v>
+        <v>132.8134763333333</v>
       </c>
       <c r="O23">
-        <v>39.98204095</v>
+        <v>39.8440429</v>
       </c>
       <c r="P23">
-        <v>93.29142888333334</v>
+        <v>92.96943343333334</v>
       </c>
       <c r="Q23">
-        <v>94.19142888333333</v>
+        <v>93.86943343333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09463218064622744</v>
+        <v>0.09509988344091261</v>
       </c>
       <c r="T23">
-        <v>0.7105677286050852</v>
+        <v>0.7173733741462773</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.79662040083003</v>
+        <v>14.12404674624684</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08192410908391183</v>
+        <v>0.08169469545730398</v>
       </c>
       <c r="C24">
-        <v>700.7201550155767</v>
+        <v>694.6544749686905</v>
       </c>
       <c r="D24">
-        <v>871.2101550155766</v>
+        <v>874.2894749686905</v>
       </c>
       <c r="E24">
-        <v>-427.51</v>
+        <v>-418.365</v>
       </c>
       <c r="F24">
-        <v>201.19</v>
+        <v>210.335</v>
       </c>
       <c r="G24">
         <v>30.7</v>
@@ -3255,28 +3255,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M24">
-        <v>10.119857</v>
+        <v>10.5798505</v>
       </c>
       <c r="N24">
-        <v>132.8134763333333</v>
+        <v>132.3534828333333</v>
       </c>
       <c r="O24">
-        <v>39.8440429</v>
+        <v>39.70604485</v>
       </c>
       <c r="P24">
-        <v>92.96943343333334</v>
+        <v>92.64743798333333</v>
       </c>
       <c r="Q24">
-        <v>93.86943343333333</v>
+        <v>93.54743798333332</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09509988344091261</v>
+        <v>0.09557973436013503</v>
       </c>
       <c r="T24">
-        <v>0.7173733741462773</v>
+        <v>0.7243557897015261</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.12404674624684</v>
+        <v>13.50995775727959</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08169469545730398</v>
+        <v>0.08146528183069612</v>
       </c>
       <c r="C25">
-        <v>694.6544749686905</v>
+        <v>688.6106400423571</v>
       </c>
       <c r="D25">
-        <v>874.2894749686905</v>
+        <v>877.3906400423571</v>
       </c>
       <c r="E25">
-        <v>-418.365</v>
+        <v>-409.22</v>
       </c>
       <c r="F25">
-        <v>210.335</v>
+        <v>219.48</v>
       </c>
       <c r="G25">
         <v>30.7</v>
@@ -3337,28 +3337,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M25">
-        <v>10.5798505</v>
+        <v>11.039844</v>
       </c>
       <c r="N25">
-        <v>132.3534828333333</v>
+        <v>131.8934893333333</v>
       </c>
       <c r="O25">
-        <v>39.70604485</v>
+        <v>39.5680468</v>
       </c>
       <c r="P25">
-        <v>92.64743798333333</v>
+        <v>92.32544253333334</v>
       </c>
       <c r="Q25">
-        <v>93.54743798333332</v>
+        <v>93.22544253333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09557973436013503</v>
+        <v>0.09607221293512648</v>
       </c>
       <c r="T25">
-        <v>0.7243557897015261</v>
+        <v>0.7315219530345449</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.50995775727959</v>
+        <v>12.94704285072627</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08146528183069612</v>
+        <v>0.08149836820408828</v>
       </c>
       <c r="C26">
-        <v>688.6106400423571</v>
+        <v>679.0170284675071</v>
       </c>
       <c r="D26">
-        <v>877.3906400423571</v>
+        <v>876.942028467507</v>
       </c>
       <c r="E26">
-        <v>-409.22</v>
+        <v>-400.075</v>
       </c>
       <c r="F26">
-        <v>219.48</v>
+        <v>228.625</v>
       </c>
       <c r="G26">
         <v>30.7</v>
@@ -3419,45 +3419,45 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M26">
-        <v>11.039844</v>
+        <v>11.842775</v>
       </c>
       <c r="N26">
-        <v>131.8934893333333</v>
+        <v>131.0905583333333</v>
       </c>
       <c r="O26">
-        <v>39.5680468</v>
+        <v>39.3271675</v>
       </c>
       <c r="P26">
-        <v>92.32544253333334</v>
+        <v>91.76339083333335</v>
       </c>
       <c r="Q26">
-        <v>93.22544253333334</v>
+        <v>92.66339083333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09607221293512648</v>
+        <v>0.0965778242721177</v>
       </c>
       <c r="T26">
-        <v>0.7315219530345449</v>
+        <v>0.7388792140564441</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>12.94704285072627</v>
+        <v>12.06924334316352</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08149836820408828</v>
+        <v>0.08127945457748041</v>
       </c>
       <c r="C27">
-        <v>679.0170284675071</v>
+        <v>672.8487876195586</v>
       </c>
       <c r="D27">
-        <v>876.942028467507</v>
+        <v>879.9187876195585</v>
       </c>
       <c r="E27">
-        <v>-400.075</v>
+        <v>-390.9300000000001</v>
       </c>
       <c r="F27">
-        <v>228.625</v>
+        <v>237.77</v>
       </c>
       <c r="G27">
         <v>30.7</v>
@@ -3501,28 +3501,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M27">
-        <v>11.842775</v>
+        <v>12.316486</v>
       </c>
       <c r="N27">
-        <v>131.0905583333333</v>
+        <v>130.6168473333333</v>
       </c>
       <c r="O27">
-        <v>39.3271675</v>
+        <v>39.1850542</v>
       </c>
       <c r="P27">
-        <v>91.76339083333335</v>
+        <v>91.43179313333334</v>
       </c>
       <c r="Q27">
-        <v>92.66339083333334</v>
+        <v>92.33179313333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0965778242721177</v>
+        <v>0.09709710078037895</v>
       </c>
       <c r="T27">
-        <v>0.7388792140564441</v>
+        <v>0.7464353199708269</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.06924334316352</v>
+        <v>11.60504167611877</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08127945457748041</v>
+        <v>0.08106054095087258</v>
       </c>
       <c r="C28">
-        <v>672.8487876195586</v>
+        <v>666.7008246827818</v>
       </c>
       <c r="D28">
-        <v>879.9187876195585</v>
+        <v>882.9158246827818</v>
       </c>
       <c r="E28">
-        <v>-390.9300000000001</v>
+        <v>-381.785</v>
       </c>
       <c r="F28">
-        <v>237.77</v>
+        <v>246.915</v>
       </c>
       <c r="G28">
         <v>30.7</v>
@@ -3583,28 +3583,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M28">
-        <v>12.316486</v>
+        <v>12.790197</v>
       </c>
       <c r="N28">
-        <v>130.6168473333333</v>
+        <v>130.1431363333333</v>
       </c>
       <c r="O28">
-        <v>39.1850542</v>
+        <v>39.0429409</v>
       </c>
       <c r="P28">
-        <v>91.43179313333334</v>
+        <v>91.10019543333334</v>
       </c>
       <c r="Q28">
-        <v>92.33179313333333</v>
+        <v>92.00019543333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09709710078037895</v>
+        <v>0.09763060404229119</v>
       </c>
       <c r="T28">
-        <v>0.7464353199708269</v>
+        <v>0.7541984424856041</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.60504167611877</v>
+        <v>11.175225317744</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08106054095087258</v>
+        <v>0.08084162732426473</v>
       </c>
       <c r="C29">
-        <v>666.7008246827818</v>
+        <v>660.5733475673517</v>
       </c>
       <c r="D29">
-        <v>882.9158246827818</v>
+        <v>885.9333475673516</v>
       </c>
       <c r="E29">
-        <v>-381.785</v>
+        <v>-372.64</v>
       </c>
       <c r="F29">
-        <v>246.915</v>
+        <v>256.06</v>
       </c>
       <c r="G29">
         <v>30.7</v>
@@ -3665,28 +3665,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M29">
-        <v>12.790197</v>
+        <v>13.263908</v>
       </c>
       <c r="N29">
-        <v>130.1431363333333</v>
+        <v>129.6694253333333</v>
       </c>
       <c r="O29">
-        <v>39.0429409</v>
+        <v>38.90082759999999</v>
       </c>
       <c r="P29">
-        <v>91.10019543333334</v>
+        <v>90.76859773333334</v>
       </c>
       <c r="Q29">
-        <v>92.00019543333333</v>
+        <v>91.66859773333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09763060404229119</v>
+        <v>0.09817892683925655</v>
       </c>
       <c r="T29">
-        <v>0.7541984424856041</v>
+        <v>0.7621772072924581</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.175225317744</v>
+        <v>10.77611012782457</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08084162732426473</v>
+        <v>0.08062271369765685</v>
       </c>
       <c r="C30">
-        <v>660.5733475673517</v>
+        <v>654.4665670354709</v>
       </c>
       <c r="D30">
-        <v>885.9333475673516</v>
+        <v>888.9715670354709</v>
       </c>
       <c r="E30">
-        <v>-372.64</v>
+        <v>-363.495</v>
       </c>
       <c r="F30">
-        <v>256.06</v>
+        <v>265.205</v>
       </c>
       <c r="G30">
         <v>30.7</v>
@@ -3747,28 +3747,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M30">
-        <v>13.263908</v>
+        <v>13.737619</v>
       </c>
       <c r="N30">
-        <v>129.6694253333333</v>
+        <v>129.1957143333333</v>
       </c>
       <c r="O30">
-        <v>38.90082759999999</v>
+        <v>38.7587143</v>
       </c>
       <c r="P30">
-        <v>90.76859773333334</v>
+        <v>90.43700003333333</v>
       </c>
       <c r="Q30">
-        <v>91.66859773333333</v>
+        <v>91.33700003333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09817892683925655</v>
+        <v>0.09874269534881247</v>
       </c>
       <c r="T30">
-        <v>0.7621772072924581</v>
+        <v>0.7703807260375335</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.77611012782457</v>
+        <v>10.40452012341682</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08062271369765685</v>
+        <v>0.080403800071049</v>
       </c>
       <c r="C31">
-        <v>654.4665670354709</v>
+        <v>648.3806967504418</v>
       </c>
       <c r="D31">
-        <v>888.9715670354709</v>
+        <v>892.0306967504416</v>
       </c>
       <c r="E31">
-        <v>-363.4950000000001</v>
+        <v>-354.3500000000001</v>
       </c>
       <c r="F31">
-        <v>265.205</v>
+        <v>274.35</v>
       </c>
       <c r="G31">
         <v>30.7</v>
@@ -3829,28 +3829,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M31">
-        <v>13.737619</v>
+        <v>14.21133</v>
       </c>
       <c r="N31">
-        <v>129.1957143333333</v>
+        <v>128.7220033333333</v>
       </c>
       <c r="O31">
-        <v>38.7587143</v>
+        <v>38.616601</v>
       </c>
       <c r="P31">
-        <v>90.43700003333333</v>
+        <v>90.10540233333333</v>
       </c>
       <c r="Q31">
-        <v>91.33700003333333</v>
+        <v>91.00540233333332</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09874269534881247</v>
+        <v>0.09932257153007001</v>
       </c>
       <c r="T31">
-        <v>0.7703807260375335</v>
+        <v>0.7788186310324681</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.40452012341683</v>
+        <v>10.0577027859696</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.080403800071049</v>
+        <v>0.08055378644444113</v>
       </c>
       <c r="C32">
-        <v>648.3806967504418</v>
+        <v>637.1375005416347</v>
       </c>
       <c r="D32">
-        <v>892.0306967504416</v>
+        <v>889.9325005416347</v>
       </c>
       <c r="E32">
-        <v>-354.3500000000001</v>
+        <v>-345.205</v>
       </c>
       <c r="F32">
-        <v>274.35</v>
+        <v>283.495</v>
       </c>
       <c r="G32">
         <v>30.7</v>
@@ -3911,45 +3911,45 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M32">
-        <v>14.21133</v>
+        <v>15.1669825</v>
       </c>
       <c r="N32">
-        <v>128.7220033333333</v>
+        <v>127.7663508333333</v>
       </c>
       <c r="O32">
-        <v>38.616601</v>
+        <v>38.32990525</v>
       </c>
       <c r="P32">
-        <v>90.10540233333333</v>
+        <v>89.43644558333334</v>
       </c>
       <c r="Q32">
-        <v>91.00540233333332</v>
+        <v>90.33644558333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09932257153007001</v>
+        <v>0.09991925571658136</v>
       </c>
       <c r="T32">
-        <v>0.7788186310324681</v>
+        <v>0.7875011129837776</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>10.0577027859696</v>
+        <v>9.423979577568138</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08055378644444113</v>
+        <v>0.08034677281783328</v>
       </c>
       <c r="C33">
-        <v>637.1375005416347</v>
+        <v>630.8910633779951</v>
       </c>
       <c r="D33">
-        <v>889.9325005416347</v>
+        <v>892.8310633779951</v>
       </c>
       <c r="E33">
-        <v>-345.205</v>
+        <v>-336.0600000000001</v>
       </c>
       <c r="F33">
-        <v>283.495</v>
+        <v>292.64</v>
       </c>
       <c r="G33">
         <v>30.7</v>
@@ -3993,28 +3993,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M33">
-        <v>15.1669825</v>
+        <v>15.65624</v>
       </c>
       <c r="N33">
-        <v>127.7663508333333</v>
+        <v>127.2770933333333</v>
       </c>
       <c r="O33">
-        <v>38.32990525</v>
+        <v>38.183128</v>
       </c>
       <c r="P33">
-        <v>89.43644558333334</v>
+        <v>89.09396533333333</v>
       </c>
       <c r="Q33">
-        <v>90.33644558333333</v>
+        <v>89.99396533333332</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09991925571658136</v>
+        <v>0.1005334894379901</v>
       </c>
       <c r="T33">
-        <v>0.7875011129837776</v>
+        <v>0.7964389620513022</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.423979577568138</v>
+        <v>9.129480215769135</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08034677281783328</v>
+        <v>0.08013975919122544</v>
       </c>
       <c r="C34">
-        <v>630.8910633779951</v>
+        <v>624.6635694952363</v>
       </c>
       <c r="D34">
-        <v>892.8310633779951</v>
+        <v>895.7485694952363</v>
       </c>
       <c r="E34">
-        <v>-336.0600000000001</v>
+        <v>-326.915</v>
       </c>
       <c r="F34">
-        <v>292.64</v>
+        <v>301.785</v>
       </c>
       <c r="G34">
         <v>30.7</v>
@@ -4075,28 +4075,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M34">
-        <v>15.65624</v>
+        <v>16.1454975</v>
       </c>
       <c r="N34">
-        <v>127.2770933333333</v>
+        <v>126.7878358333333</v>
       </c>
       <c r="O34">
-        <v>38.183128</v>
+        <v>38.03635075</v>
       </c>
       <c r="P34">
-        <v>89.09396533333333</v>
+        <v>88.75148508333334</v>
       </c>
       <c r="Q34">
-        <v>89.99396533333332</v>
+        <v>89.65148508333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1005334894379901</v>
+        <v>0.1011660584943663</v>
       </c>
       <c r="T34">
-        <v>0.7964389620513022</v>
+        <v>0.8056436125835291</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.129480215769135</v>
+        <v>8.852829300139764</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08013975919122544</v>
+        <v>0.07993274556461757</v>
       </c>
       <c r="C35">
-        <v>624.6635694952363</v>
+        <v>618.4552052051774</v>
       </c>
       <c r="D35">
-        <v>895.7485694952363</v>
+        <v>898.6852052051773</v>
       </c>
       <c r="E35">
-        <v>-326.915</v>
+        <v>-317.77</v>
       </c>
       <c r="F35">
-        <v>301.785</v>
+        <v>310.93</v>
       </c>
       <c r="G35">
         <v>30.7</v>
@@ -4157,28 +4157,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M35">
-        <v>16.1454975</v>
+        <v>16.634755</v>
       </c>
       <c r="N35">
-        <v>126.7878358333333</v>
+        <v>126.2985783333333</v>
       </c>
       <c r="O35">
-        <v>38.03635075</v>
+        <v>37.8895735</v>
       </c>
       <c r="P35">
-        <v>88.75148508333334</v>
+        <v>88.40900483333334</v>
       </c>
       <c r="Q35">
-        <v>89.65148508333333</v>
+        <v>89.30900483333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1011660584943663</v>
+        <v>0.1018177963100266</v>
       </c>
       <c r="T35">
-        <v>0.8056436125835291</v>
+        <v>0.8151271919197626</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.852829300139764</v>
+        <v>8.592451967782715</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07993274556461757</v>
+        <v>0.07972573193800972</v>
       </c>
       <c r="C36">
-        <v>618.4552052051774</v>
+        <v>612.266159270903</v>
       </c>
       <c r="D36">
-        <v>898.6852052051773</v>
+        <v>901.641159270903</v>
       </c>
       <c r="E36">
-        <v>-317.77</v>
+        <v>-308.625</v>
       </c>
       <c r="F36">
-        <v>310.93</v>
+        <v>320.075</v>
       </c>
       <c r="G36">
         <v>30.7</v>
@@ -4239,28 +4239,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M36">
-        <v>16.634755</v>
+        <v>17.1240125</v>
       </c>
       <c r="N36">
-        <v>126.2985783333333</v>
+        <v>125.8093208333333</v>
       </c>
       <c r="O36">
-        <v>37.8895735</v>
+        <v>37.74279625</v>
       </c>
       <c r="P36">
-        <v>88.40900483333334</v>
+        <v>88.06652458333333</v>
       </c>
       <c r="Q36">
-        <v>89.30900483333333</v>
+        <v>88.96652458333332</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1018177963100266</v>
+        <v>0.102489587596938</v>
       </c>
       <c r="T36">
-        <v>0.8151271919197626</v>
+        <v>0.8249025736971112</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.592451967782715</v>
+        <v>8.346953340131778</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07972573193800972</v>
+        <v>0.07951871831140186</v>
       </c>
       <c r="C37">
-        <v>612.266159270903</v>
+        <v>606.0966229472118</v>
       </c>
       <c r="D37">
-        <v>901.641159270903</v>
+        <v>904.6166229472118</v>
       </c>
       <c r="E37">
-        <v>-308.625</v>
+        <v>-299.48</v>
       </c>
       <c r="F37">
-        <v>320.075</v>
+        <v>329.22</v>
       </c>
       <c r="G37">
         <v>30.7</v>
@@ -4321,28 +4321,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M37">
-        <v>17.1240125</v>
+        <v>17.61327</v>
       </c>
       <c r="N37">
-        <v>125.8093208333333</v>
+        <v>125.3200633333333</v>
       </c>
       <c r="O37">
-        <v>37.74279625</v>
+        <v>37.596019</v>
       </c>
       <c r="P37">
-        <v>88.06652458333333</v>
+        <v>87.72404433333334</v>
       </c>
       <c r="Q37">
-        <v>88.96652458333332</v>
+        <v>88.62404433333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.102489587596938</v>
+        <v>0.1031823723615654</v>
       </c>
       <c r="T37">
-        <v>0.8249025736971112</v>
+        <v>0.8349834361550018</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.346953340131778</v>
+        <v>8.115093525128119</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07951871831140188</v>
+        <v>0.07931170468479401</v>
       </c>
       <c r="C38">
-        <v>606.0966229472117</v>
+        <v>599.9467900218639</v>
       </c>
       <c r="D38">
-        <v>904.6166229472116</v>
+        <v>907.6117900218638</v>
       </c>
       <c r="E38">
-        <v>-299.4800000000001</v>
+        <v>-290.335</v>
       </c>
       <c r="F38">
-        <v>329.22</v>
+        <v>338.365</v>
       </c>
       <c r="G38">
         <v>30.7</v>
@@ -4403,28 +4403,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M38">
-        <v>17.61327</v>
+        <v>18.1025275</v>
       </c>
       <c r="N38">
-        <v>125.3200633333333</v>
+        <v>124.8308058333333</v>
       </c>
       <c r="O38">
-        <v>37.596019</v>
+        <v>37.44924175</v>
       </c>
       <c r="P38">
-        <v>87.72404433333334</v>
+        <v>87.38156408333333</v>
       </c>
       <c r="Q38">
-        <v>88.62404433333333</v>
+        <v>88.28156408333332</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1031823723615654</v>
+        <v>0.1038971502933238</v>
       </c>
       <c r="T38">
-        <v>0.8349834361550018</v>
+        <v>0.845384325992508</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.11509352512812</v>
+        <v>7.895766673097628</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07931170468479401</v>
+        <v>0.07910469105818617</v>
       </c>
       <c r="C39">
-        <v>599.9467900218639</v>
+        <v>593.8168568576556</v>
       </c>
       <c r="D39">
-        <v>907.6117900218638</v>
+        <v>910.6268568576555</v>
       </c>
       <c r="E39">
-        <v>-290.335</v>
+        <v>-281.1900000000001</v>
       </c>
       <c r="F39">
-        <v>338.365</v>
+        <v>347.51</v>
       </c>
       <c r="G39">
         <v>30.7</v>
@@ -4485,28 +4485,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M39">
-        <v>18.1025275</v>
+        <v>18.591785</v>
       </c>
       <c r="N39">
-        <v>124.8308058333333</v>
+        <v>124.3415483333333</v>
       </c>
       <c r="O39">
-        <v>37.44924175</v>
+        <v>37.3024645</v>
       </c>
       <c r="P39">
-        <v>87.38156408333333</v>
+        <v>87.03908383333334</v>
       </c>
       <c r="Q39">
-        <v>88.28156408333332</v>
+        <v>87.93908383333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1038971502933238</v>
+        <v>0.1046349855777196</v>
       </c>
       <c r="T39">
-        <v>0.845384325992508</v>
+        <v>0.8561207284054178</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.895766673097628</v>
+        <v>7.687983339595061</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07910469105818617</v>
+        <v>0.07911607743157832</v>
       </c>
       <c r="C40">
-        <v>593.8168568576556</v>
+        <v>584.5054985817349</v>
       </c>
       <c r="D40">
-        <v>910.6268568576555</v>
+        <v>910.4604985817348</v>
       </c>
       <c r="E40">
-        <v>-281.1900000000001</v>
+        <v>-272.045</v>
       </c>
       <c r="F40">
-        <v>347.51</v>
+        <v>356.655</v>
       </c>
       <c r="G40">
         <v>30.7</v>
@@ -4567,45 +4567,45 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M40">
-        <v>18.591785</v>
+        <v>19.3663665</v>
       </c>
       <c r="N40">
-        <v>124.3415483333333</v>
+        <v>123.5669668333333</v>
       </c>
       <c r="O40">
-        <v>37.3024645</v>
+        <v>37.07009005</v>
       </c>
       <c r="P40">
-        <v>87.03908383333334</v>
+        <v>86.49687678333333</v>
       </c>
       <c r="Q40">
-        <v>87.93908383333333</v>
+        <v>87.39687678333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1046349855777196</v>
+        <v>0.1053970121829153</v>
       </c>
       <c r="T40">
-        <v>0.8561207284054178</v>
+        <v>0.8672091440121933</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.687983339595061</v>
+        <v>7.380493048777804</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07911607743157832</v>
+        <v>0.07891466380497046</v>
       </c>
       <c r="C41">
-        <v>584.5054985817349</v>
+        <v>578.3122120553699</v>
       </c>
       <c r="D41">
-        <v>910.4604985817348</v>
+        <v>913.4122120553698</v>
       </c>
       <c r="E41">
-        <v>-272.045</v>
+        <v>-262.9</v>
       </c>
       <c r="F41">
-        <v>356.655</v>
+        <v>365.8</v>
       </c>
       <c r="G41">
         <v>30.7</v>
@@ -4649,28 +4649,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M41">
-        <v>19.3663665</v>
+        <v>19.86294</v>
       </c>
       <c r="N41">
-        <v>123.5669668333333</v>
+        <v>123.0703933333333</v>
       </c>
       <c r="O41">
-        <v>37.07009005</v>
+        <v>36.921118</v>
       </c>
       <c r="P41">
-        <v>86.49687678333333</v>
+        <v>86.14927533333332</v>
       </c>
       <c r="Q41">
-        <v>87.39687678333333</v>
+        <v>87.04927533333331</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1053970121829153</v>
+        <v>0.1061844396749508</v>
       </c>
       <c r="T41">
-        <v>0.8672091440121933</v>
+        <v>0.8786671734725282</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.380493048777804</v>
+        <v>7.195980722558359</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07891466380497046</v>
+        <v>0.07871325017836261</v>
       </c>
       <c r="C42">
-        <v>578.3122120553699</v>
+        <v>572.1381266928357</v>
       </c>
       <c r="D42">
-        <v>913.4122120553698</v>
+        <v>916.3831266928357</v>
       </c>
       <c r="E42">
-        <v>-262.9</v>
+        <v>-253.755</v>
       </c>
       <c r="F42">
-        <v>365.8</v>
+        <v>374.9450000000001</v>
       </c>
       <c r="G42">
         <v>30.7</v>
@@ -4731,28 +4731,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M42">
-        <v>19.86294</v>
+        <v>20.3595135</v>
       </c>
       <c r="N42">
-        <v>123.0703933333333</v>
+        <v>122.5738198333333</v>
       </c>
       <c r="O42">
-        <v>36.921118</v>
+        <v>36.77214595</v>
       </c>
       <c r="P42">
-        <v>86.14927533333332</v>
+        <v>85.80167388333334</v>
       </c>
       <c r="Q42">
-        <v>87.04927533333331</v>
+        <v>86.70167388333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1061844396749508</v>
+        <v>0.1069985596243434</v>
       </c>
       <c r="T42">
-        <v>0.8786671734725282</v>
+        <v>0.8905136107111793</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.195980722558359</v>
+        <v>7.02046899761791</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07871325017836261</v>
+        <v>0.07851183655175475</v>
       </c>
       <c r="C43">
-        <v>572.1381266928357</v>
+        <v>565.9834304634795</v>
       </c>
       <c r="D43">
-        <v>916.3831266928357</v>
+        <v>919.3734304634795</v>
       </c>
       <c r="E43">
-        <v>-253.755</v>
+        <v>-244.61</v>
       </c>
       <c r="F43">
-        <v>374.9450000000001</v>
+        <v>384.09</v>
       </c>
       <c r="G43">
         <v>30.7</v>
@@ -4813,28 +4813,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M43">
-        <v>20.3595135</v>
+        <v>20.856087</v>
       </c>
       <c r="N43">
-        <v>122.5738198333333</v>
+        <v>122.0772463333333</v>
       </c>
       <c r="O43">
-        <v>36.77214595</v>
+        <v>36.6231739</v>
       </c>
       <c r="P43">
-        <v>85.80167388333334</v>
+        <v>85.45407243333334</v>
       </c>
       <c r="Q43">
-        <v>86.70167388333333</v>
+        <v>86.35407243333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1069985596243434</v>
+        <v>0.1078407526754392</v>
       </c>
       <c r="T43">
-        <v>0.8905136107111793</v>
+        <v>0.902768545785646</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.02046899761791</v>
+        <v>6.853314973865103</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07851183655175475</v>
+        <v>0.07831042292514691</v>
       </c>
       <c r="C44">
-        <v>565.9834304634796</v>
+        <v>559.8483137981756</v>
       </c>
       <c r="D44">
-        <v>919.3734304634795</v>
+        <v>922.3833137981755</v>
       </c>
       <c r="E44">
-        <v>-244.6100000000001</v>
+        <v>-235.465</v>
       </c>
       <c r="F44">
-        <v>384.09</v>
+        <v>393.235</v>
       </c>
       <c r="G44">
         <v>30.7</v>
@@ -4895,28 +4895,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M44">
-        <v>20.856087</v>
+        <v>21.3526605</v>
       </c>
       <c r="N44">
-        <v>122.0772463333333</v>
+        <v>121.5806728333333</v>
       </c>
       <c r="O44">
-        <v>36.6231739</v>
+        <v>36.47420185</v>
       </c>
       <c r="P44">
-        <v>85.45407243333334</v>
+        <v>85.10647098333334</v>
       </c>
       <c r="Q44">
-        <v>86.35407243333333</v>
+        <v>86.00647098333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1078407526754392</v>
+        <v>0.1087124963599068</v>
       </c>
       <c r="T44">
-        <v>0.9027685457856459</v>
+        <v>0.9154534785820237</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.853314973865104</v>
+        <v>6.693935555868241</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07831042292514691</v>
+        <v>0.07810900929853903</v>
       </c>
       <c r="C45">
-        <v>559.8483137981756</v>
+        <v>553.7329696297525</v>
       </c>
       <c r="D45">
-        <v>922.3833137981755</v>
+        <v>925.4129696297524</v>
       </c>
       <c r="E45">
-        <v>-235.465</v>
+        <v>-226.3200000000001</v>
       </c>
       <c r="F45">
-        <v>393.235</v>
+        <v>402.38</v>
       </c>
       <c r="G45">
         <v>30.7</v>
@@ -4977,28 +4977,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M45">
-        <v>21.3526605</v>
+        <v>21.849234</v>
       </c>
       <c r="N45">
-        <v>121.5806728333333</v>
+        <v>121.0840993333333</v>
       </c>
       <c r="O45">
-        <v>36.47420185</v>
+        <v>36.3252298</v>
       </c>
       <c r="P45">
-        <v>85.10647098333334</v>
+        <v>84.75886953333334</v>
       </c>
       <c r="Q45">
-        <v>86.00647098333333</v>
+        <v>85.65886953333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1087124963599068</v>
+        <v>0.1096153737473911</v>
       </c>
       <c r="T45">
-        <v>0.9154534785820237</v>
+        <v>0.9285914446925579</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.693935555868241</v>
+        <v>6.541800656871236</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07810900929853903</v>
+        <v>0.0779075956719312</v>
       </c>
       <c r="C46">
-        <v>553.7329696297525</v>
+        <v>547.6375934342157</v>
       </c>
       <c r="D46">
-        <v>925.4129696297524</v>
+        <v>928.4625934342156</v>
       </c>
       <c r="E46">
-        <v>-226.3200000000001</v>
+        <v>-217.175</v>
       </c>
       <c r="F46">
-        <v>402.38</v>
+        <v>411.525</v>
       </c>
       <c r="G46">
         <v>30.7</v>
@@ -5059,28 +5059,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M46">
-        <v>21.849234</v>
+        <v>22.3458075</v>
       </c>
       <c r="N46">
-        <v>121.0840993333333</v>
+        <v>120.5875258333333</v>
       </c>
       <c r="O46">
-        <v>36.3252298</v>
+        <v>36.17625775</v>
       </c>
       <c r="P46">
-        <v>84.75886953333334</v>
+        <v>84.41126808333334</v>
       </c>
       <c r="Q46">
-        <v>85.65886953333333</v>
+        <v>85.31126808333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1096153737473911</v>
+        <v>0.1105510830398749</v>
       </c>
       <c r="T46">
-        <v>0.9285914446925579</v>
+        <v>0.9422071550252936</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.541800656871236</v>
+        <v>6.396427308940763</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0779075956719312</v>
+        <v>0.07770618204532334</v>
       </c>
       <c r="C47">
-        <v>547.6375934342157</v>
+        <v>541.5623832727931</v>
       </c>
       <c r="D47">
-        <v>928.4625934342156</v>
+        <v>931.5323832727931</v>
       </c>
       <c r="E47">
-        <v>-217.175</v>
+        <v>-208.03</v>
       </c>
       <c r="F47">
-        <v>411.525</v>
+        <v>420.67</v>
       </c>
       <c r="G47">
         <v>30.7</v>
@@ -5141,28 +5141,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M47">
-        <v>22.3458075</v>
+        <v>22.842381</v>
       </c>
       <c r="N47">
-        <v>120.5875258333333</v>
+        <v>120.0909523333333</v>
       </c>
       <c r="O47">
-        <v>36.17625775</v>
+        <v>36.0272857</v>
       </c>
       <c r="P47">
-        <v>84.41126808333334</v>
+        <v>84.06366663333333</v>
       </c>
       <c r="Q47">
-        <v>85.31126808333333</v>
+        <v>84.96366663333332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1105510830398749</v>
+        <v>0.1115214482320803</v>
       </c>
       <c r="T47">
-        <v>0.9422071550252936</v>
+        <v>0.956327150925908</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.396427308940763</v>
+        <v>6.257374541355095</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07770618204532334</v>
+        <v>0.07750476841871548</v>
       </c>
       <c r="C48">
-        <v>541.5623832727931</v>
+        <v>535.5075398348129</v>
       </c>
       <c r="D48">
-        <v>931.5323832727931</v>
+        <v>934.6225398348129</v>
       </c>
       <c r="E48">
-        <v>-208.03</v>
+        <v>-198.885</v>
       </c>
       <c r="F48">
-        <v>420.67</v>
+        <v>429.8150000000001</v>
       </c>
       <c r="G48">
         <v>30.7</v>
@@ -5223,28 +5223,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M48">
-        <v>22.842381</v>
+        <v>23.3389545</v>
       </c>
       <c r="N48">
-        <v>120.0909523333333</v>
+        <v>119.5943788333333</v>
       </c>
       <c r="O48">
-        <v>36.0272857</v>
+        <v>35.87831365</v>
       </c>
       <c r="P48">
-        <v>84.06366663333333</v>
+        <v>83.71606518333334</v>
       </c>
       <c r="Q48">
-        <v>84.96366663333332</v>
+        <v>84.61606518333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1115214482320803</v>
+        <v>0.1125284309787085</v>
       </c>
       <c r="T48">
-        <v>0.956327150925908</v>
+        <v>0.9709799768605081</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.257374541355095</v>
+        <v>6.124238912815624</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07750476841871548</v>
+        <v>0.07763935479210764</v>
       </c>
       <c r="C49">
-        <v>535.5075398348129</v>
+        <v>524.295402124115</v>
       </c>
       <c r="D49">
-        <v>934.6225398348129</v>
+        <v>932.5554021241149</v>
       </c>
       <c r="E49">
-        <v>-198.885</v>
+        <v>-189.74</v>
       </c>
       <c r="F49">
-        <v>429.8150000000001</v>
+        <v>438.96</v>
       </c>
       <c r="G49">
         <v>30.7</v>
@@ -5305,45 +5305,45 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M49">
-        <v>23.3389545</v>
+        <v>24.274488</v>
       </c>
       <c r="N49">
-        <v>119.5943788333333</v>
+        <v>118.6588453333333</v>
       </c>
       <c r="O49">
-        <v>35.87831365</v>
+        <v>35.5976536</v>
       </c>
       <c r="P49">
-        <v>83.71606518333334</v>
+        <v>83.06119173333333</v>
       </c>
       <c r="Q49">
-        <v>84.61606518333333</v>
+        <v>83.96119173333332</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1125284309787085</v>
+        <v>0.1135741438309762</v>
       </c>
       <c r="T49">
-        <v>0.9709799768605081</v>
+        <v>0.9861963730233619</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.124238912815624</v>
+        <v>5.88821207406448</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07763935479210764</v>
+        <v>0.07744494116549977</v>
       </c>
       <c r="C50">
-        <v>524.2954021241151</v>
+        <v>518.1393832051893</v>
       </c>
       <c r="D50">
-        <v>932.5554021241149</v>
+        <v>935.5443832051893</v>
       </c>
       <c r="E50">
-        <v>-189.7400000000001</v>
+        <v>-180.595</v>
       </c>
       <c r="F50">
-        <v>438.96</v>
+        <v>448.105</v>
       </c>
       <c r="G50">
         <v>30.7</v>
@@ -5387,28 +5387,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M50">
-        <v>24.274488</v>
+        <v>24.7802065</v>
       </c>
       <c r="N50">
-        <v>118.6588453333333</v>
+        <v>118.1531268333333</v>
       </c>
       <c r="O50">
-        <v>35.5976536</v>
+        <v>35.44593805</v>
       </c>
       <c r="P50">
-        <v>83.06119173333335</v>
+        <v>82.70718878333334</v>
       </c>
       <c r="Q50">
-        <v>83.96119173333334</v>
+        <v>83.60718878333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1135741438309762</v>
+        <v>0.1146608650303917</v>
       </c>
       <c r="T50">
-        <v>0.9861963730233619</v>
+        <v>1.002009490604367</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.888212074064481</v>
+        <v>5.768044480716225</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07744494116549977</v>
+        <v>0.07725052753889192</v>
       </c>
       <c r="C51">
-        <v>518.1393832051893</v>
+        <v>512.0025861679939</v>
       </c>
       <c r="D51">
-        <v>935.5443832051893</v>
+        <v>938.5525861679938</v>
       </c>
       <c r="E51">
-        <v>-180.595</v>
+        <v>-171.45</v>
       </c>
       <c r="F51">
-        <v>448.105</v>
+        <v>457.25</v>
       </c>
       <c r="G51">
         <v>30.7</v>
@@ -5469,28 +5469,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M51">
-        <v>24.7802065</v>
+        <v>25.285925</v>
       </c>
       <c r="N51">
-        <v>118.1531268333333</v>
+        <v>117.6474083333333</v>
       </c>
       <c r="O51">
-        <v>35.44593805</v>
+        <v>35.2942225</v>
       </c>
       <c r="P51">
-        <v>82.70718878333334</v>
+        <v>82.35318583333333</v>
       </c>
       <c r="Q51">
-        <v>83.60718878333333</v>
+        <v>83.25318583333332</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1146608650303917</v>
+        <v>0.1157910550777838</v>
       </c>
       <c r="T51">
-        <v>1.002009490604367</v>
+        <v>1.018455132888612</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.768044480716225</v>
+        <v>5.6526835911019</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07725052753889192</v>
+        <v>0.07705611391228408</v>
       </c>
       <c r="C52">
-        <v>512.0025861679939</v>
+        <v>505.8851970320833</v>
       </c>
       <c r="D52">
-        <v>938.5525861679938</v>
+        <v>941.5801970320832</v>
       </c>
       <c r="E52">
-        <v>-171.45</v>
+        <v>-162.3050000000001</v>
       </c>
       <c r="F52">
-        <v>457.25</v>
+        <v>466.395</v>
       </c>
       <c r="G52">
         <v>30.7</v>
@@ -5551,28 +5551,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M52">
-        <v>25.285925</v>
+        <v>25.7916435</v>
       </c>
       <c r="N52">
-        <v>117.6474083333333</v>
+        <v>117.1416898333333</v>
       </c>
       <c r="O52">
-        <v>35.2942225</v>
+        <v>35.14250695</v>
       </c>
       <c r="P52">
-        <v>82.35318583333333</v>
+        <v>81.99918288333333</v>
       </c>
       <c r="Q52">
-        <v>83.25318583333332</v>
+        <v>82.89918288333332</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1157910550777838</v>
+        <v>0.116967375331192</v>
       </c>
       <c r="T52">
-        <v>1.018455132888612</v>
+        <v>1.035572025878337</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.6526835911019</v>
+        <v>5.541846657943041</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07705611391228408</v>
+        <v>0.07686170028567621</v>
       </c>
       <c r="C53">
-        <v>505.8851970320833</v>
+        <v>499.7874042250501</v>
       </c>
       <c r="D53">
-        <v>941.5801970320832</v>
+        <v>944.6274042250501</v>
       </c>
       <c r="E53">
-        <v>-162.3050000000001</v>
+        <v>-153.16</v>
       </c>
       <c r="F53">
-        <v>466.395</v>
+        <v>475.54</v>
       </c>
       <c r="G53">
         <v>30.7</v>
@@ -5633,28 +5633,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M53">
-        <v>25.7916435</v>
+        <v>26.297362</v>
       </c>
       <c r="N53">
-        <v>117.1416898333333</v>
+        <v>116.6359713333333</v>
       </c>
       <c r="O53">
-        <v>35.14250695</v>
+        <v>34.9907914</v>
       </c>
       <c r="P53">
-        <v>81.99918288333333</v>
+        <v>81.64517993333334</v>
       </c>
       <c r="Q53">
-        <v>82.89918288333332</v>
+        <v>82.54517993333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.116967375331192</v>
+        <v>0.1181927089284921</v>
       </c>
       <c r="T53">
-        <v>1.035572025878337</v>
+        <v>1.053402122742633</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.541846657943041</v>
+        <v>5.435272683751827</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07686170028567621</v>
+        <v>0.07666728665906836</v>
       </c>
       <c r="C54">
-        <v>499.7874042250501</v>
+        <v>493.7093986216151</v>
       </c>
       <c r="D54">
-        <v>944.6274042250501</v>
+        <v>947.6943986216151</v>
       </c>
       <c r="E54">
-        <v>-153.16</v>
+        <v>-144.015</v>
       </c>
       <c r="F54">
-        <v>475.54</v>
+        <v>484.685</v>
       </c>
       <c r="G54">
         <v>30.7</v>
@@ -5715,28 +5715,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M54">
-        <v>26.297362</v>
+        <v>26.8030805</v>
       </c>
       <c r="N54">
-        <v>116.6359713333333</v>
+        <v>116.1302528333333</v>
       </c>
       <c r="O54">
-        <v>34.9907914</v>
+        <v>34.83907585</v>
       </c>
       <c r="P54">
-        <v>81.64517993333334</v>
+        <v>81.29117698333334</v>
       </c>
       <c r="Q54">
-        <v>82.54517993333333</v>
+        <v>82.19117698333334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1181927089284921</v>
+        <v>0.1194701843809965</v>
       </c>
       <c r="T54">
-        <v>1.053402122742633</v>
+        <v>1.07199094713307</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.435272683751827</v>
+        <v>5.332720368964058</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07666728665906836</v>
+        <v>0.0764728730324605</v>
       </c>
       <c r="C55">
-        <v>493.7093986216151</v>
+        <v>487.651373583485</v>
       </c>
       <c r="D55">
-        <v>947.6943986216151</v>
+        <v>950.781373583485</v>
       </c>
       <c r="E55">
-        <v>-144.015</v>
+        <v>-134.87</v>
       </c>
       <c r="F55">
-        <v>484.685</v>
+        <v>493.83</v>
       </c>
       <c r="G55">
         <v>30.7</v>
@@ -5797,28 +5797,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M55">
-        <v>26.8030805</v>
+        <v>27.308799</v>
       </c>
       <c r="N55">
-        <v>116.1302528333333</v>
+        <v>115.6245343333333</v>
       </c>
       <c r="O55">
-        <v>34.83907585</v>
+        <v>34.68736029999999</v>
       </c>
       <c r="P55">
-        <v>81.29117698333334</v>
+        <v>80.93717403333333</v>
       </c>
       <c r="Q55">
-        <v>82.19117698333334</v>
+        <v>81.83717403333333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1194701843809965</v>
+        <v>0.1208032022444794</v>
       </c>
       <c r="T55">
-        <v>1.07199094713307</v>
+        <v>1.091387981279612</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.332720368964058</v>
+        <v>5.233966288057315</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0764728730324605</v>
+        <v>0.07627845940585265</v>
       </c>
       <c r="C56">
-        <v>487.651373583485</v>
+        <v>481.6135249999888</v>
       </c>
       <c r="D56">
-        <v>950.781373583485</v>
+        <v>953.8885249999888</v>
       </c>
       <c r="E56">
-        <v>-134.87</v>
+        <v>-125.725</v>
       </c>
       <c r="F56">
-        <v>493.83</v>
+        <v>502.975</v>
       </c>
       <c r="G56">
         <v>30.7</v>
@@ -5879,28 +5879,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M56">
-        <v>27.308799</v>
+        <v>27.8145175</v>
       </c>
       <c r="N56">
-        <v>115.6245343333333</v>
+        <v>115.1188158333333</v>
       </c>
       <c r="O56">
-        <v>34.68736029999999</v>
+        <v>34.53564475</v>
       </c>
       <c r="P56">
-        <v>80.93717403333333</v>
+        <v>80.58317108333334</v>
       </c>
       <c r="Q56">
-        <v>81.83717403333333</v>
+        <v>81.48317108333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1208032022444794</v>
+        <v>0.1221954653463392</v>
       </c>
       <c r="T56">
-        <v>1.091387981279612</v>
+        <v>1.111647105832668</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.233966288057315</v>
+        <v>5.138803264638092</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07627845940585265</v>
+        <v>0.07608404577924481</v>
       </c>
       <c r="C57">
-        <v>481.6135249999888</v>
+        <v>475.5960513295149</v>
       </c>
       <c r="D57">
-        <v>953.8885249999888</v>
+        <v>957.0160513295149</v>
       </c>
       <c r="E57">
-        <v>-125.725</v>
+        <v>-116.58</v>
       </c>
       <c r="F57">
-        <v>502.975</v>
+        <v>512.12</v>
       </c>
       <c r="G57">
         <v>30.7</v>
@@ -5961,28 +5961,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M57">
-        <v>27.8145175</v>
+        <v>28.320236</v>
       </c>
       <c r="N57">
-        <v>115.1188158333333</v>
+        <v>114.6130973333333</v>
       </c>
       <c r="O57">
-        <v>34.53564475</v>
+        <v>34.3839292</v>
       </c>
       <c r="P57">
-        <v>80.58317108333334</v>
+        <v>80.22916813333333</v>
       </c>
       <c r="Q57">
-        <v>81.48317108333333</v>
+        <v>81.12916813333332</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1221954653463392</v>
+        <v>0.1236510131346473</v>
       </c>
       <c r="T57">
-        <v>1.111647105832668</v>
+        <v>1.13282709968359</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.138803264638092</v>
+        <v>5.047038920626697</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07608404577924481</v>
+        <v>0.07588963215263694</v>
       </c>
       <c r="C58">
-        <v>475.5960513295149</v>
+        <v>469.599153641766</v>
       </c>
       <c r="D58">
-        <v>957.0160513295149</v>
+        <v>960.164153641766</v>
       </c>
       <c r="E58">
-        <v>-116.58</v>
+        <v>-107.4349999999999</v>
       </c>
       <c r="F58">
-        <v>512.12</v>
+        <v>521.2650000000001</v>
       </c>
       <c r="G58">
         <v>30.7</v>
@@ -6043,28 +6043,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M58">
-        <v>28.320236</v>
+        <v>28.82595450000001</v>
       </c>
       <c r="N58">
-        <v>114.6130973333333</v>
+        <v>114.1073788333333</v>
       </c>
       <c r="O58">
-        <v>34.3839292</v>
+        <v>34.23221365</v>
       </c>
       <c r="P58">
-        <v>80.22916813333333</v>
+        <v>79.87516518333334</v>
       </c>
       <c r="Q58">
-        <v>81.12916813333332</v>
+        <v>80.77516518333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1236510131346473</v>
+        <v>0.1251742608200859</v>
       </c>
       <c r="T58">
-        <v>1.13282709968359</v>
+        <v>1.154992209527578</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.047038920626697</v>
+        <v>4.958494378159561</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07588963215263694</v>
+        <v>0.07569521852602909</v>
       </c>
       <c r="C59">
-        <v>469.599153641766</v>
+        <v>463.6230356608484</v>
       </c>
       <c r="D59">
-        <v>960.164153641766</v>
+        <v>963.3330356608484</v>
       </c>
       <c r="E59">
-        <v>-107.4349999999999</v>
+        <v>-98.28999999999996</v>
       </c>
       <c r="F59">
-        <v>521.2650000000001</v>
+        <v>530.4100000000001</v>
       </c>
       <c r="G59">
         <v>30.7</v>
@@ -6125,28 +6125,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M59">
-        <v>28.82595450000001</v>
+        <v>29.33167300000001</v>
       </c>
       <c r="N59">
-        <v>114.1073788333333</v>
+        <v>113.6016603333333</v>
       </c>
       <c r="O59">
-        <v>34.23221365</v>
+        <v>34.0804981</v>
       </c>
       <c r="P59">
-        <v>79.87516518333334</v>
+        <v>79.52116223333333</v>
       </c>
       <c r="Q59">
-        <v>80.77516518333333</v>
+        <v>80.42116223333332</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1251742608200859</v>
+        <v>0.1267700441095931</v>
       </c>
       <c r="T59">
-        <v>1.154992209527578</v>
+        <v>1.178212800792708</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.958494378159561</v>
+        <v>4.8730030957775</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0756952185260291</v>
+        <v>0.07550080489942124</v>
       </c>
       <c r="C60">
-        <v>463.6230356608482</v>
+        <v>457.6679038092227</v>
       </c>
       <c r="D60">
-        <v>963.3330356608482</v>
+        <v>966.5229038092226</v>
       </c>
       <c r="E60">
-        <v>-98.29000000000008</v>
+        <v>-89.1450000000001</v>
       </c>
       <c r="F60">
-        <v>530.41</v>
+        <v>539.5549999999999</v>
       </c>
       <c r="G60">
         <v>30.7</v>
@@ -6207,28 +6207,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M60">
-        <v>29.331673</v>
+        <v>29.8373915</v>
       </c>
       <c r="N60">
-        <v>113.6016603333333</v>
+        <v>113.0959418333333</v>
       </c>
       <c r="O60">
-        <v>34.0804981</v>
+        <v>33.92878255</v>
       </c>
       <c r="P60">
-        <v>79.52116223333334</v>
+        <v>79.16715928333335</v>
       </c>
       <c r="Q60">
-        <v>80.42116223333333</v>
+        <v>80.06715928333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1267700441095931</v>
+        <v>0.1284436704863933</v>
       </c>
       <c r="T60">
-        <v>1.178212800792708</v>
+        <v>1.202566103826869</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.873003095777501</v>
+        <v>4.790409822967713</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07550080489942124</v>
+        <v>0.07530639127281338</v>
       </c>
       <c r="C61">
-        <v>457.6679038092227</v>
+        <v>451.7339672525243</v>
       </c>
       <c r="D61">
-        <v>966.5229038092226</v>
+        <v>969.7339672525242</v>
       </c>
       <c r="E61">
-        <v>-89.1450000000001</v>
+        <v>-80.00000000000011</v>
       </c>
       <c r="F61">
-        <v>539.5549999999999</v>
+        <v>548.6999999999999</v>
       </c>
       <c r="G61">
         <v>30.7</v>
@@ -6289,28 +6289,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M61">
-        <v>29.8373915</v>
+        <v>30.34311</v>
       </c>
       <c r="N61">
-        <v>113.0959418333333</v>
+        <v>112.5902233333333</v>
       </c>
       <c r="O61">
-        <v>33.92878255</v>
+        <v>33.777067</v>
       </c>
       <c r="P61">
-        <v>79.16715928333335</v>
+        <v>78.81315633333334</v>
       </c>
       <c r="Q61">
-        <v>80.06715928333334</v>
+        <v>79.71315633333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1284436704863933</v>
+        <v>0.1302009781820335</v>
       </c>
       <c r="T61">
-        <v>1.202566103826869</v>
+        <v>1.228137072012738</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.790409822967713</v>
+        <v>4.710569659251584</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07530639127281338</v>
+        <v>0.07511197764620553</v>
       </c>
       <c r="C62">
-        <v>451.7339672525243</v>
+        <v>445.8214379452851</v>
       </c>
       <c r="D62">
-        <v>969.7339672525242</v>
+        <v>972.9664379452851</v>
       </c>
       <c r="E62">
-        <v>-80.00000000000011</v>
+        <v>-70.85500000000002</v>
       </c>
       <c r="F62">
-        <v>548.6999999999999</v>
+        <v>557.845</v>
       </c>
       <c r="G62">
         <v>30.7</v>
@@ -6371,28 +6371,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M62">
-        <v>30.34311</v>
+        <v>30.8488285</v>
       </c>
       <c r="N62">
-        <v>112.5902233333333</v>
+        <v>112.0845048333333</v>
       </c>
       <c r="O62">
-        <v>33.777067</v>
+        <v>33.62535145</v>
       </c>
       <c r="P62">
-        <v>78.81315633333334</v>
+        <v>78.45915338333333</v>
       </c>
       <c r="Q62">
-        <v>79.71315633333333</v>
+        <v>79.35915338333332</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1302009781820335</v>
+        <v>0.1320484042210398</v>
       </c>
       <c r="T62">
-        <v>1.228137072012738</v>
+        <v>1.255019371900446</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.710569659251584</v>
+        <v>4.63334720582123</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07511197764620553</v>
+        <v>0.07491756401959768</v>
       </c>
       <c r="C63">
-        <v>445.8214379452851</v>
+        <v>439.9305306775705</v>
       </c>
       <c r="D63">
-        <v>972.9664379452851</v>
+        <v>976.2205306775704</v>
       </c>
       <c r="E63">
-        <v>-70.85500000000002</v>
+        <v>-61.71000000000004</v>
       </c>
       <c r="F63">
-        <v>557.845</v>
+        <v>566.99</v>
       </c>
       <c r="G63">
         <v>30.7</v>
@@ -6453,28 +6453,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M63">
-        <v>30.8488285</v>
+        <v>31.354547</v>
       </c>
       <c r="N63">
-        <v>112.0845048333333</v>
+        <v>111.5787863333333</v>
       </c>
       <c r="O63">
-        <v>33.62535145</v>
+        <v>33.4736359</v>
       </c>
       <c r="P63">
-        <v>78.45915338333333</v>
+        <v>78.10515043333334</v>
       </c>
       <c r="Q63">
-        <v>79.35915338333332</v>
+        <v>79.00515043333333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1320484042210398</v>
+        <v>0.1339930632094676</v>
       </c>
       <c r="T63">
-        <v>1.255019371900446</v>
+        <v>1.283316529676982</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.63334720582123</v>
+        <v>4.558615799275726</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07491756401959768</v>
+        <v>0.07582565039298983</v>
       </c>
       <c r="C64">
-        <v>439.9305306775705</v>
+        <v>415.7697324931569</v>
       </c>
       <c r="D64">
-        <v>976.2205306775704</v>
+        <v>961.2047324931568</v>
       </c>
       <c r="E64">
-        <v>-61.71000000000004</v>
+        <v>-52.56500000000005</v>
       </c>
       <c r="F64">
-        <v>566.99</v>
+        <v>576.135</v>
       </c>
       <c r="G64">
         <v>30.7</v>
@@ -6535,45 +6535,45 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M64">
-        <v>31.354547</v>
+        <v>33.300603</v>
       </c>
       <c r="N64">
-        <v>111.5787863333333</v>
+        <v>109.6327303333333</v>
       </c>
       <c r="O64">
-        <v>33.4736359</v>
+        <v>32.8898191</v>
       </c>
       <c r="P64">
-        <v>78.10515043333334</v>
+        <v>76.74291123333333</v>
       </c>
       <c r="Q64">
-        <v>79.00515043333333</v>
+        <v>77.64291123333332</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1339930632094676</v>
+        <v>0.1360428388999725</v>
       </c>
       <c r="T64">
-        <v>1.283316529676982</v>
+        <v>1.313143263549546</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.3</v>
       </c>
       <c r="W64">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.558615799275726</v>
+        <v>4.292214568406864</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07582565039298983</v>
+        <v>0.07564873676638197</v>
       </c>
       <c r="C65">
-        <v>415.7697324931569</v>
+        <v>409.5137747278563</v>
       </c>
       <c r="D65">
-        <v>961.2047324931568</v>
+        <v>964.0937747278563</v>
       </c>
       <c r="E65">
-        <v>-52.56500000000005</v>
+        <v>-43.42000000000007</v>
       </c>
       <c r="F65">
-        <v>576.135</v>
+        <v>585.28</v>
       </c>
       <c r="G65">
         <v>30.7</v>
@@ -6617,28 +6617,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M65">
-        <v>33.300603</v>
+        <v>33.829184</v>
       </c>
       <c r="N65">
-        <v>109.6327303333333</v>
+        <v>109.1041493333333</v>
       </c>
       <c r="O65">
-        <v>32.8898191</v>
+        <v>32.7312448</v>
       </c>
       <c r="P65">
-        <v>76.74291123333333</v>
+        <v>76.37290453333334</v>
       </c>
       <c r="Q65">
-        <v>77.64291123333332</v>
+        <v>77.27290453333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1360428388999725</v>
+        <v>0.1382064910177277</v>
       </c>
       <c r="T65">
-        <v>1.313143263549546</v>
+        <v>1.344627038192808</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.292214568406864</v>
+        <v>4.225148715775507</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07564873676638197</v>
+        <v>0.07547182313977412</v>
       </c>
       <c r="C66">
-        <v>409.5137747278563</v>
+        <v>403.2752362015782</v>
       </c>
       <c r="D66">
-        <v>964.0937747278563</v>
+        <v>967.0002362015782</v>
       </c>
       <c r="E66">
-        <v>-43.42000000000007</v>
+        <v>-34.27499999999998</v>
       </c>
       <c r="F66">
-        <v>585.28</v>
+        <v>594.4250000000001</v>
       </c>
       <c r="G66">
         <v>30.7</v>
@@ -6699,28 +6699,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M66">
-        <v>33.829184</v>
+        <v>34.35776500000001</v>
       </c>
       <c r="N66">
-        <v>109.1041493333333</v>
+        <v>108.5755683333333</v>
       </c>
       <c r="O66">
-        <v>32.7312448</v>
+        <v>32.5726705</v>
       </c>
       <c r="P66">
-        <v>76.37290453333334</v>
+        <v>76.00289783333334</v>
       </c>
       <c r="Q66">
-        <v>77.27290453333333</v>
+        <v>76.90289783333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1382064910177277</v>
+        <v>0.1404937803993546</v>
       </c>
       <c r="T66">
-        <v>1.344627038192808</v>
+        <v>1.377909885672828</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.225148715775507</v>
+        <v>4.160146427840498</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07547182313977412</v>
+        <v>0.07529490951316627</v>
       </c>
       <c r="C67">
-        <v>403.2752362015782</v>
+        <v>397.0542749324732</v>
       </c>
       <c r="D67">
-        <v>967.0002362015782</v>
+        <v>969.9242749324732</v>
       </c>
       <c r="E67">
-        <v>-34.27499999999998</v>
+        <v>-25.13</v>
       </c>
       <c r="F67">
-        <v>594.4250000000001</v>
+        <v>603.5700000000001</v>
       </c>
       <c r="G67">
         <v>30.7</v>
@@ -6781,28 +6781,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M67">
-        <v>34.35776500000001</v>
+        <v>34.886346</v>
       </c>
       <c r="N67">
-        <v>108.5755683333333</v>
+        <v>108.0469873333333</v>
       </c>
       <c r="O67">
-        <v>32.5726705</v>
+        <v>32.4140962</v>
       </c>
       <c r="P67">
-        <v>76.00289783333334</v>
+        <v>75.63289113333335</v>
       </c>
       <c r="Q67">
-        <v>76.90289783333333</v>
+        <v>76.53289113333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1404937803993546</v>
+        <v>0.1429156162151949</v>
       </c>
       <c r="T67">
-        <v>1.377909885672828</v>
+        <v>1.413150547710496</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.160146427840498</v>
+        <v>4.097113906206552</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07529490951316627</v>
+        <v>0.0751179958865584</v>
       </c>
       <c r="C68">
-        <v>397.0542749324732</v>
+        <v>390.8510508557648</v>
       </c>
       <c r="D68">
-        <v>969.9242749324732</v>
+        <v>972.8660508557648</v>
       </c>
       <c r="E68">
-        <v>-25.13</v>
+        <v>-15.98500000000001</v>
       </c>
       <c r="F68">
-        <v>603.5700000000001</v>
+        <v>612.715</v>
       </c>
       <c r="G68">
         <v>30.7</v>
@@ -6863,28 +6863,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M68">
-        <v>34.886346</v>
+        <v>35.41492700000001</v>
       </c>
       <c r="N68">
-        <v>108.0469873333333</v>
+        <v>107.5184063333333</v>
       </c>
       <c r="O68">
-        <v>32.4140962</v>
+        <v>32.2555219</v>
       </c>
       <c r="P68">
-        <v>75.63289113333335</v>
+        <v>75.26288443333334</v>
       </c>
       <c r="Q68">
-        <v>76.53289113333334</v>
+        <v>76.16288443333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1429156162151949</v>
+        <v>0.1454842299592679</v>
       </c>
       <c r="T68">
-        <v>1.413150547710496</v>
+        <v>1.450527007447417</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.097113906206552</v>
+        <v>4.035962952382573</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0751179958865584</v>
+        <v>0.07660708225995055</v>
       </c>
       <c r="C69">
-        <v>390.8510508557648</v>
+        <v>357.4882026550674</v>
       </c>
       <c r="D69">
-        <v>972.8660508557648</v>
+        <v>948.6482026550674</v>
       </c>
       <c r="E69">
-        <v>-15.98500000000001</v>
+        <v>-6.840000000000032</v>
       </c>
       <c r="F69">
-        <v>612.715</v>
+        <v>621.86</v>
       </c>
       <c r="G69">
         <v>30.7</v>
@@ -6945,45 +6945,45 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M69">
-        <v>35.41492700000001</v>
+        <v>38.120018</v>
       </c>
       <c r="N69">
-        <v>107.5184063333333</v>
+        <v>104.8133153333333</v>
       </c>
       <c r="O69">
-        <v>32.2555219</v>
+        <v>31.4439946</v>
       </c>
       <c r="P69">
-        <v>75.26288443333334</v>
+        <v>73.36932073333334</v>
       </c>
       <c r="Q69">
-        <v>76.16288443333333</v>
+        <v>74.26932073333333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1454842299592679</v>
+        <v>0.1482133820623455</v>
       </c>
       <c r="T69">
-        <v>1.450527007447417</v>
+        <v>1.490239495917896</v>
       </c>
       <c r="U69">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.3</v>
       </c>
       <c r="W69">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.035962952382573</v>
+        <v>3.749561013673533</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07660708225995055</v>
+        <v>0.07645466863334272</v>
       </c>
       <c r="C70">
-        <v>357.4882026550674</v>
+        <v>350.766460131199</v>
       </c>
       <c r="D70">
-        <v>948.6482026550674</v>
+        <v>951.071460131199</v>
       </c>
       <c r="E70">
-        <v>-6.840000000000032</v>
+        <v>2.305000000000064</v>
       </c>
       <c r="F70">
-        <v>621.86</v>
+        <v>631.0050000000001</v>
       </c>
       <c r="G70">
         <v>30.7</v>
@@ -7027,28 +7027,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M70">
-        <v>38.120018</v>
+        <v>38.68060650000001</v>
       </c>
       <c r="N70">
-        <v>104.8133153333333</v>
+        <v>104.2527268333333</v>
       </c>
       <c r="O70">
-        <v>31.4439946</v>
+        <v>31.27581805</v>
       </c>
       <c r="P70">
-        <v>73.36932073333334</v>
+        <v>72.97690878333333</v>
       </c>
       <c r="Q70">
-        <v>74.26932073333333</v>
+        <v>73.87690878333332</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1482133820623455</v>
+        <v>0.1511186084946539</v>
       </c>
       <c r="T70">
-        <v>1.490239495917896</v>
+        <v>1.532514080418728</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.749561013673533</v>
+        <v>3.695219549707249</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07645466863334272</v>
+        <v>0.07630225500673485</v>
       </c>
       <c r="C71">
-        <v>350.766460131199</v>
+        <v>344.0571294060808</v>
       </c>
       <c r="D71">
-        <v>951.071460131199</v>
+        <v>953.5071294060808</v>
       </c>
       <c r="E71">
-        <v>2.305000000000064</v>
+        <v>11.45000000000005</v>
       </c>
       <c r="F71">
-        <v>631.0050000000001</v>
+        <v>640.1500000000001</v>
       </c>
       <c r="G71">
         <v>30.7</v>
@@ -7109,28 +7109,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M71">
-        <v>38.68060650000001</v>
+        <v>39.241195</v>
       </c>
       <c r="N71">
-        <v>104.2527268333333</v>
+        <v>103.6921383333333</v>
       </c>
       <c r="O71">
-        <v>31.27581805</v>
+        <v>31.1076415</v>
       </c>
       <c r="P71">
-        <v>72.97690878333333</v>
+        <v>72.58449683333333</v>
       </c>
       <c r="Q71">
-        <v>73.87690878333332</v>
+        <v>73.48449683333332</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1511186084946539</v>
+        <v>0.1542175166891162</v>
       </c>
       <c r="T71">
-        <v>1.532514080418728</v>
+        <v>1.577606970552949</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.695219549707249</v>
+        <v>3.642430698997146</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07630225500673485</v>
+        <v>0.07614984138012698</v>
       </c>
       <c r="C72">
-        <v>344.0571294060808</v>
+        <v>337.3603060834319</v>
       </c>
       <c r="D72">
-        <v>953.5071294060808</v>
+        <v>955.9553060834319</v>
       </c>
       <c r="E72">
-        <v>11.45000000000005</v>
+        <v>20.59500000000003</v>
       </c>
       <c r="F72">
-        <v>640.1500000000001</v>
+        <v>649.2950000000001</v>
       </c>
       <c r="G72">
         <v>30.7</v>
@@ -7191,28 +7191,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M72">
-        <v>39.241195</v>
+        <v>39.80178350000001</v>
       </c>
       <c r="N72">
-        <v>103.6921383333333</v>
+        <v>103.1315498333333</v>
       </c>
       <c r="O72">
-        <v>31.1076415</v>
+        <v>30.93946495</v>
       </c>
       <c r="P72">
-        <v>72.58449683333333</v>
+        <v>72.19208488333334</v>
       </c>
       <c r="Q72">
-        <v>73.48449683333332</v>
+        <v>73.09208488333333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1542175166891162</v>
+        <v>0.1575301426900931</v>
       </c>
       <c r="T72">
-        <v>1.577606970552949</v>
+        <v>1.625809715179184</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.642430698997146</v>
+        <v>3.591128858166201</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.076149841380127</v>
+        <v>0.07599742775351914</v>
       </c>
       <c r="C73">
-        <v>337.3603060834319</v>
+        <v>330.6760867513688</v>
       </c>
       <c r="D73">
-        <v>955.9553060834318</v>
+        <v>958.4160867513687</v>
       </c>
       <c r="E73">
-        <v>20.59499999999991</v>
+        <v>29.7399999999999</v>
       </c>
       <c r="F73">
-        <v>649.295</v>
+        <v>658.4399999999999</v>
       </c>
       <c r="G73">
         <v>30.7</v>
@@ -7273,28 +7273,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M73">
-        <v>39.8017835</v>
+        <v>40.36237199999999</v>
       </c>
       <c r="N73">
-        <v>103.1315498333333</v>
+        <v>102.5709613333333</v>
       </c>
       <c r="O73">
-        <v>30.93946495</v>
+        <v>30.7712884</v>
       </c>
       <c r="P73">
-        <v>72.19208488333334</v>
+        <v>71.79967293333334</v>
       </c>
       <c r="Q73">
-        <v>73.09208488333333</v>
+        <v>72.69967293333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1575301426900931</v>
+        <v>0.1610793848339969</v>
       </c>
       <c r="T73">
-        <v>1.625809715179184</v>
+        <v>1.677455512993008</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.591128858166201</v>
+        <v>3.541252068469449</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07599742775351914</v>
+        <v>0.07727581412691129</v>
       </c>
       <c r="C74">
-        <v>330.6760867513688</v>
+        <v>301.2752274673969</v>
       </c>
       <c r="D74">
-        <v>958.4160867513687</v>
+        <v>938.1602274673969</v>
       </c>
       <c r="E74">
-        <v>29.7399999999999</v>
+        <v>38.88499999999999</v>
       </c>
       <c r="F74">
-        <v>658.4399999999999</v>
+        <v>667.585</v>
       </c>
       <c r="G74">
         <v>30.7</v>
@@ -7355,45 +7355,45 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M74">
-        <v>40.36237199999999</v>
+        <v>42.7921985</v>
       </c>
       <c r="N74">
-        <v>102.5709613333333</v>
+        <v>100.1411348333333</v>
       </c>
       <c r="O74">
-        <v>30.7712884</v>
+        <v>30.04234045</v>
       </c>
       <c r="P74">
-        <v>71.79967293333334</v>
+        <v>70.09879438333333</v>
       </c>
       <c r="Q74">
-        <v>72.69967293333333</v>
+        <v>70.99879438333332</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1610793848339969</v>
+        <v>0.1648915338033751</v>
       </c>
       <c r="T74">
-        <v>1.677455512993008</v>
+        <v>1.732926925459708</v>
       </c>
       <c r="U74">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V74">
         <v>0.3</v>
       </c>
       <c r="W74">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.541252068469449</v>
+        <v>3.340172703053182</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07727581412691129</v>
+        <v>0.07714300050030343</v>
       </c>
       <c r="C75">
-        <v>301.2752274673969</v>
+        <v>294.194698221437</v>
       </c>
       <c r="D75">
-        <v>938.1602274673969</v>
+        <v>940.2246982214369</v>
       </c>
       <c r="E75">
-        <v>38.88499999999999</v>
+        <v>48.02999999999997</v>
       </c>
       <c r="F75">
-        <v>667.585</v>
+        <v>676.73</v>
       </c>
       <c r="G75">
         <v>30.7</v>
@@ -7437,28 +7437,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M75">
-        <v>42.7921985</v>
+        <v>43.378393</v>
       </c>
       <c r="N75">
-        <v>100.1411348333333</v>
+        <v>99.55494033333333</v>
       </c>
       <c r="O75">
-        <v>30.04234045</v>
+        <v>29.8664821</v>
       </c>
       <c r="P75">
-        <v>70.09879438333333</v>
+        <v>69.68845823333334</v>
       </c>
       <c r="Q75">
-        <v>70.99879438333332</v>
+        <v>70.58845823333333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1648915338033751</v>
+        <v>0.168996925001167</v>
       </c>
       <c r="T75">
-        <v>1.732926925459708</v>
+        <v>1.792665369654616</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.340172703053182</v>
+        <v>3.295035234093004</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07714300050030343</v>
+        <v>0.07701018687369557</v>
       </c>
       <c r="C76">
-        <v>294.194698221437</v>
+        <v>287.1232749658923</v>
       </c>
       <c r="D76">
-        <v>940.2246982214369</v>
+        <v>942.2982749658922</v>
       </c>
       <c r="E76">
-        <v>48.02999999999997</v>
+        <v>57.17499999999995</v>
       </c>
       <c r="F76">
-        <v>676.73</v>
+        <v>685.875</v>
       </c>
       <c r="G76">
         <v>30.7</v>
@@ -7519,28 +7519,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M76">
-        <v>43.378393</v>
+        <v>43.9645875</v>
       </c>
       <c r="N76">
-        <v>99.55494033333333</v>
+        <v>98.96874583333334</v>
       </c>
       <c r="O76">
-        <v>29.8664821</v>
+        <v>29.69062375</v>
       </c>
       <c r="P76">
-        <v>69.68845823333334</v>
+        <v>69.27812208333334</v>
       </c>
       <c r="Q76">
-        <v>70.58845823333333</v>
+        <v>70.17812208333334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.168996925001167</v>
+        <v>0.1734307474947823</v>
       </c>
       <c r="T76">
-        <v>1.792665369654616</v>
+        <v>1.857182889385116</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.295035234093004</v>
+        <v>3.251101430971764</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07701018687369557</v>
+        <v>0.07687737324708772</v>
       </c>
       <c r="C77">
-        <v>287.1232749658923</v>
+        <v>280.0610180811308</v>
       </c>
       <c r="D77">
-        <v>942.2982749658922</v>
+        <v>944.3810180811307</v>
       </c>
       <c r="E77">
-        <v>57.17499999999995</v>
+        <v>66.31999999999994</v>
       </c>
       <c r="F77">
-        <v>685.875</v>
+        <v>695.02</v>
       </c>
       <c r="G77">
         <v>30.7</v>
@@ -7601,28 +7601,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M77">
-        <v>43.9645875</v>
+        <v>44.55078200000001</v>
       </c>
       <c r="N77">
-        <v>98.96874583333334</v>
+        <v>98.38255133333334</v>
       </c>
       <c r="O77">
-        <v>29.69062375</v>
+        <v>29.5147654</v>
       </c>
       <c r="P77">
-        <v>69.27812208333334</v>
+        <v>68.86778593333334</v>
       </c>
       <c r="Q77">
-        <v>70.17812208333334</v>
+        <v>69.76778593333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1734307474947823</v>
+        <v>0.1782340551961989</v>
       </c>
       <c r="T77">
-        <v>1.857182889385116</v>
+        <v>1.927076869093158</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.251101430971764</v>
+        <v>3.208323780564241</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07687737324708772</v>
+        <v>0.07674455962047987</v>
       </c>
       <c r="C78">
-        <v>280.0610180811308</v>
+        <v>273.0079884825336</v>
       </c>
       <c r="D78">
-        <v>944.3810180811307</v>
+        <v>946.4729884825335</v>
       </c>
       <c r="E78">
-        <v>66.31999999999994</v>
+        <v>75.46499999999992</v>
       </c>
       <c r="F78">
-        <v>695.02</v>
+        <v>704.165</v>
       </c>
       <c r="G78">
         <v>30.7</v>
@@ -7683,28 +7683,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M78">
-        <v>44.55078200000001</v>
+        <v>45.1369765</v>
       </c>
       <c r="N78">
-        <v>98.38255133333334</v>
+        <v>97.79635683333333</v>
       </c>
       <c r="O78">
-        <v>29.5147654</v>
+        <v>29.33890705</v>
       </c>
       <c r="P78">
-        <v>68.86778593333334</v>
+        <v>68.45744978333333</v>
       </c>
       <c r="Q78">
-        <v>69.76778593333333</v>
+        <v>69.35744978333332</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1782340551961989</v>
+        <v>0.1834550418281733</v>
       </c>
       <c r="T78">
-        <v>1.927076869093158</v>
+        <v>2.003048586167117</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.208323780564241</v>
+        <v>3.166657237959511</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07674455962047987</v>
+        <v>0.07661174599387202</v>
       </c>
       <c r="C79">
-        <v>273.0079884825336</v>
+        <v>265.9642476264319</v>
       </c>
       <c r="D79">
-        <v>946.4729884825335</v>
+        <v>948.5742476264319</v>
       </c>
       <c r="E79">
-        <v>75.46499999999992</v>
+        <v>84.61000000000001</v>
       </c>
       <c r="F79">
-        <v>704.165</v>
+        <v>713.3100000000001</v>
       </c>
       <c r="G79">
         <v>30.7</v>
@@ -7765,28 +7765,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M79">
-        <v>45.1369765</v>
+        <v>45.72317100000001</v>
       </c>
       <c r="N79">
-        <v>97.79635683333333</v>
+        <v>97.21016233333333</v>
       </c>
       <c r="O79">
-        <v>29.33890705</v>
+        <v>29.1630487</v>
       </c>
       <c r="P79">
-        <v>68.45744978333333</v>
+        <v>68.04711363333334</v>
       </c>
       <c r="Q79">
-        <v>69.35744978333332</v>
+        <v>68.94711363333333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1834550418281733</v>
+        <v>0.1891506636085092</v>
       </c>
       <c r="T79">
-        <v>2.003048586167117</v>
+        <v>2.085926822975072</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.166657237959511</v>
+        <v>3.126059068242081</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07661174599387202</v>
+        <v>0.07647893236726416</v>
       </c>
       <c r="C80">
-        <v>265.9642476264319</v>
+        <v>258.9298575161283</v>
       </c>
       <c r="D80">
-        <v>948.5742476264319</v>
+        <v>950.6848575161283</v>
       </c>
       <c r="E80">
-        <v>84.61000000000001</v>
+        <v>93.755</v>
       </c>
       <c r="F80">
-        <v>713.3100000000001</v>
+        <v>722.455</v>
       </c>
       <c r="G80">
         <v>30.7</v>
@@ -7847,28 +7847,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M80">
-        <v>45.72317100000001</v>
+        <v>46.30936550000001</v>
       </c>
       <c r="N80">
-        <v>97.21016233333333</v>
+        <v>96.62396783333332</v>
       </c>
       <c r="O80">
-        <v>29.1630487</v>
+        <v>28.98719035</v>
       </c>
       <c r="P80">
-        <v>68.04711363333334</v>
+        <v>67.63677748333333</v>
       </c>
       <c r="Q80">
-        <v>68.94711363333333</v>
+        <v>68.53677748333332</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1891506636085092</v>
+        <v>0.1953887255584008</v>
       </c>
       <c r="T80">
-        <v>2.085926822975072</v>
+        <v>2.176698225193308</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.126059068242081</v>
+        <v>3.086488700289649</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07647893236726416</v>
+        <v>0.0763461187406563</v>
       </c>
       <c r="C81">
-        <v>258.9298575161283</v>
+        <v>251.9048807079926</v>
       </c>
       <c r="D81">
-        <v>950.6848575161283</v>
+        <v>952.8048807079925</v>
       </c>
       <c r="E81">
-        <v>93.755</v>
+        <v>102.9</v>
       </c>
       <c r="F81">
-        <v>722.455</v>
+        <v>731.6</v>
       </c>
       <c r="G81">
         <v>30.7</v>
@@ -7929,28 +7929,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M81">
-        <v>46.30936550000001</v>
+        <v>46.89556</v>
       </c>
       <c r="N81">
-        <v>96.62396783333332</v>
+        <v>96.03777333333333</v>
       </c>
       <c r="O81">
-        <v>28.98719035</v>
+        <v>28.811332</v>
       </c>
       <c r="P81">
-        <v>67.63677748333333</v>
+        <v>67.22644133333333</v>
       </c>
       <c r="Q81">
-        <v>68.53677748333332</v>
+        <v>68.12644133333332</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1953887255584008</v>
+        <v>0.2022505937032816</v>
       </c>
       <c r="T81">
-        <v>2.176698225193308</v>
+        <v>2.276546767633369</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.086488700289649</v>
+        <v>3.047907591536029</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0763461187406563</v>
+        <v>0.07621330511404845</v>
       </c>
       <c r="C82">
-        <v>251.9048807079926</v>
+        <v>244.8893803176439</v>
       </c>
       <c r="D82">
-        <v>952.8048807079925</v>
+        <v>954.9343803176439</v>
       </c>
       <c r="E82">
-        <v>102.9</v>
+        <v>112.045</v>
       </c>
       <c r="F82">
-        <v>731.6</v>
+        <v>740.745</v>
       </c>
       <c r="G82">
         <v>30.7</v>
@@ -8011,28 +8011,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M82">
-        <v>46.89556</v>
+        <v>47.4817545</v>
       </c>
       <c r="N82">
-        <v>96.03777333333333</v>
+        <v>95.45157883333334</v>
       </c>
       <c r="O82">
-        <v>28.811332</v>
+        <v>28.63547365</v>
       </c>
       <c r="P82">
-        <v>67.22644133333333</v>
+        <v>66.81610518333335</v>
       </c>
       <c r="Q82">
-        <v>68.12644133333332</v>
+        <v>67.71610518333334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2022505937032816</v>
+        <v>0.2098347637581498</v>
       </c>
       <c r="T82">
-        <v>2.276546767633369</v>
+        <v>2.386905682961856</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.047907591536029</v>
+        <v>3.010279102751634</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07621330511404845</v>
+        <v>0.0805576914874406</v>
       </c>
       <c r="C83">
-        <v>244.8893803176439</v>
+        <v>170.6880037686486</v>
       </c>
       <c r="D83">
-        <v>954.9343803176439</v>
+        <v>889.8780037686487</v>
       </c>
       <c r="E83">
-        <v>112.045</v>
+        <v>121.1900000000001</v>
       </c>
       <c r="F83">
-        <v>740.745</v>
+        <v>749.8900000000001</v>
       </c>
       <c r="G83">
         <v>30.7</v>
@@ -8093,45 +8093,45 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M83">
-        <v>47.4817545</v>
+        <v>53.91709100000001</v>
       </c>
       <c r="N83">
-        <v>95.45157883333334</v>
+        <v>89.01624233333332</v>
       </c>
       <c r="O83">
-        <v>28.63547365</v>
+        <v>26.7048727</v>
       </c>
       <c r="P83">
-        <v>66.81610518333335</v>
+        <v>62.31136963333333</v>
       </c>
       <c r="Q83">
-        <v>67.71610518333334</v>
+        <v>63.21136963333332</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2098347637581498</v>
+        <v>0.2182616193746701</v>
       </c>
       <c r="T83">
-        <v>2.386905682961856</v>
+        <v>2.509526699993509</v>
       </c>
       <c r="U83">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V83">
         <v>0.3</v>
       </c>
       <c r="W83">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.010279102751634</v>
+        <v>2.650983773092159</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0805576914874406</v>
+        <v>0.08047947786083275</v>
       </c>
       <c r="C84">
-        <v>170.6880037686486</v>
+        <v>162.6357864070677</v>
       </c>
       <c r="D84">
-        <v>889.8780037686487</v>
+        <v>890.9707864070677</v>
       </c>
       <c r="E84">
-        <v>121.1900000000001</v>
+        <v>130.335</v>
       </c>
       <c r="F84">
-        <v>749.8900000000001</v>
+        <v>759.0350000000001</v>
       </c>
       <c r="G84">
         <v>30.7</v>
@@ -8175,28 +8175,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M84">
-        <v>53.91709100000001</v>
+        <v>54.57461650000001</v>
       </c>
       <c r="N84">
-        <v>89.01624233333332</v>
+        <v>88.35871683333332</v>
       </c>
       <c r="O84">
-        <v>26.7048727</v>
+        <v>26.50761504999999</v>
       </c>
       <c r="P84">
-        <v>62.31136963333333</v>
+        <v>61.85110178333332</v>
       </c>
       <c r="Q84">
-        <v>63.21136963333332</v>
+        <v>62.75110178333331</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2182616193746701</v>
+        <v>0.2276798697696045</v>
       </c>
       <c r="T84">
-        <v>2.509526699993509</v>
+        <v>2.646573719028885</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.650983773092159</v>
+        <v>2.619044209560928</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08047947786083275</v>
+        <v>0.08040126423422489</v>
       </c>
       <c r="C85">
-        <v>162.6357864070677</v>
+        <v>154.5862562501486</v>
       </c>
       <c r="D85">
-        <v>890.9707864070677</v>
+        <v>892.0662562501486</v>
       </c>
       <c r="E85">
-        <v>130.335</v>
+        <v>139.48</v>
       </c>
       <c r="F85">
-        <v>759.0350000000001</v>
+        <v>768.1800000000001</v>
       </c>
       <c r="G85">
         <v>30.7</v>
@@ -8257,28 +8257,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M85">
-        <v>54.57461650000001</v>
+        <v>55.23214200000001</v>
       </c>
       <c r="N85">
-        <v>88.35871683333332</v>
+        <v>87.70119133333333</v>
       </c>
       <c r="O85">
-        <v>26.50761504999999</v>
+        <v>26.3103574</v>
       </c>
       <c r="P85">
-        <v>61.85110178333332</v>
+        <v>61.39083393333333</v>
       </c>
       <c r="Q85">
-        <v>62.75110178333331</v>
+        <v>62.29083393333332</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2276798697696045</v>
+        <v>0.2382754014639057</v>
       </c>
       <c r="T85">
-        <v>2.646573719028885</v>
+        <v>2.800751615443685</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.619044209560928</v>
+        <v>2.58786511182806</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08040126423422489</v>
+        <v>0.08032305060761705</v>
       </c>
       <c r="C86">
-        <v>154.5862562501487</v>
+        <v>146.5394232220401</v>
       </c>
       <c r="D86">
-        <v>892.0662562501486</v>
+        <v>893.16442322204</v>
       </c>
       <c r="E86">
-        <v>139.4799999999999</v>
+        <v>148.6249999999999</v>
       </c>
       <c r="F86">
-        <v>768.1799999999999</v>
+        <v>777.3249999999999</v>
       </c>
       <c r="G86">
         <v>30.7</v>
@@ -8339,28 +8339,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M86">
-        <v>55.232142</v>
+        <v>55.8896675</v>
       </c>
       <c r="N86">
-        <v>87.70119133333333</v>
+        <v>87.04366583333334</v>
       </c>
       <c r="O86">
-        <v>26.3103574</v>
+        <v>26.11309975</v>
       </c>
       <c r="P86">
-        <v>61.39083393333333</v>
+        <v>60.93056608333333</v>
       </c>
       <c r="Q86">
-        <v>62.29083393333332</v>
+        <v>61.83056608333332</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2382754014639056</v>
+        <v>0.2502836707174469</v>
       </c>
       <c r="T86">
-        <v>2.800751615443683</v>
+        <v>2.975486564713788</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.58786511182806</v>
+        <v>2.557419639924201</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08032305060761705</v>
+        <v>0.08024483698100918</v>
       </c>
       <c r="C87">
-        <v>146.5394232220401</v>
+        <v>138.4952972958193</v>
       </c>
       <c r="D87">
-        <v>893.16442322204</v>
+        <v>894.2652972958193</v>
       </c>
       <c r="E87">
-        <v>148.6249999999999</v>
+        <v>157.77</v>
       </c>
       <c r="F87">
-        <v>777.3249999999999</v>
+        <v>786.47</v>
       </c>
       <c r="G87">
         <v>30.7</v>
@@ -8421,28 +8421,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M87">
-        <v>55.8896675</v>
+        <v>56.54719300000001</v>
       </c>
       <c r="N87">
-        <v>87.04366583333334</v>
+        <v>86.38614033333333</v>
       </c>
       <c r="O87">
-        <v>26.11309975</v>
+        <v>25.9158421</v>
       </c>
       <c r="P87">
-        <v>60.93056608333333</v>
+        <v>60.47029823333333</v>
       </c>
       <c r="Q87">
-        <v>61.83056608333332</v>
+        <v>61.37029823333332</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2502836707174469</v>
+        <v>0.2640074070072084</v>
       </c>
       <c r="T87">
-        <v>2.975486564713788</v>
+        <v>3.175183649593908</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.557419639924201</v>
+        <v>2.527682202250664</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08024483698100918</v>
+        <v>0.08254172335440133</v>
       </c>
       <c r="C88">
-        <v>138.4952972958193</v>
+        <v>98.11197606282758</v>
       </c>
       <c r="D88">
-        <v>894.2652972958193</v>
+        <v>863.0269760628275</v>
       </c>
       <c r="E88">
-        <v>157.77</v>
+        <v>166.915</v>
       </c>
       <c r="F88">
-        <v>786.47</v>
+        <v>795.615</v>
       </c>
       <c r="G88">
         <v>30.7</v>
@@ -8503,45 +8503,45 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M88">
-        <v>56.54719300000001</v>
+        <v>60.30761700000001</v>
       </c>
       <c r="N88">
-        <v>86.38614033333333</v>
+        <v>82.62571633333333</v>
       </c>
       <c r="O88">
-        <v>25.9158421</v>
+        <v>24.7877149</v>
       </c>
       <c r="P88">
-        <v>60.47029823333333</v>
+        <v>57.83800143333333</v>
       </c>
       <c r="Q88">
-        <v>61.37029823333332</v>
+        <v>58.73800143333332</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2640074070072084</v>
+        <v>0.2798424873415487</v>
       </c>
       <c r="T88">
-        <v>3.175183649593908</v>
+        <v>3.405603362917123</v>
       </c>
       <c r="U88">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V88">
         <v>0.3</v>
       </c>
       <c r="W88">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.527682202250664</v>
+        <v>2.370070986776568</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08254172335440133</v>
+        <v>0.08249080972779349</v>
       </c>
       <c r="C89">
-        <v>98.11197606282758</v>
+        <v>89.63574579791418</v>
       </c>
       <c r="D89">
-        <v>863.0269760628275</v>
+        <v>863.6957457979141</v>
       </c>
       <c r="E89">
-        <v>166.915</v>
+        <v>176.0599999999999</v>
       </c>
       <c r="F89">
-        <v>795.615</v>
+        <v>804.76</v>
       </c>
       <c r="G89">
         <v>30.7</v>
@@ -8585,28 +8585,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M89">
-        <v>60.30761700000001</v>
+        <v>61.00080800000001</v>
       </c>
       <c r="N89">
-        <v>82.62571633333333</v>
+        <v>81.93252533333333</v>
       </c>
       <c r="O89">
-        <v>24.7877149</v>
+        <v>24.5797576</v>
       </c>
       <c r="P89">
-        <v>57.83800143333333</v>
+        <v>57.35276773333334</v>
       </c>
       <c r="Q89">
-        <v>58.73800143333332</v>
+        <v>58.25276773333333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2798424873415487</v>
+        <v>0.2983167477316124</v>
       </c>
       <c r="T89">
-        <v>3.405603362917123</v>
+        <v>3.674426361794209</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.370070986776568</v>
+        <v>2.343138361926834</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08249080972779349</v>
+        <v>0.08243989610118563</v>
       </c>
       <c r="C90">
-        <v>89.63574579791418</v>
+        <v>81.16055281183787</v>
       </c>
       <c r="D90">
-        <v>863.6957457979141</v>
+        <v>864.3655528118378</v>
       </c>
       <c r="E90">
-        <v>176.0599999999999</v>
+        <v>185.2049999999999</v>
       </c>
       <c r="F90">
-        <v>804.76</v>
+        <v>813.905</v>
       </c>
       <c r="G90">
         <v>30.7</v>
@@ -8667,28 +8667,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M90">
-        <v>61.00080800000001</v>
+        <v>61.69399900000001</v>
       </c>
       <c r="N90">
-        <v>81.93252533333333</v>
+        <v>81.23933433333333</v>
       </c>
       <c r="O90">
-        <v>24.5797576</v>
+        <v>24.3718003</v>
       </c>
       <c r="P90">
-        <v>57.35276773333334</v>
+        <v>56.86753403333333</v>
       </c>
       <c r="Q90">
-        <v>58.25276773333333</v>
+        <v>57.76753403333332</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2983167477316124</v>
+        <v>0.320149964556233</v>
       </c>
       <c r="T90">
-        <v>3.674426361794209</v>
+        <v>3.992126269558036</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.343138361926834</v>
+        <v>2.316810964601814</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08243989610118563</v>
+        <v>0.08238898247457777</v>
       </c>
       <c r="C91">
-        <v>81.16055281183787</v>
+        <v>72.68639951974001</v>
       </c>
       <c r="D91">
-        <v>864.3655528118378</v>
+        <v>865.03639951974</v>
       </c>
       <c r="E91">
-        <v>185.2049999999999</v>
+        <v>194.35</v>
       </c>
       <c r="F91">
-        <v>813.905</v>
+        <v>823.0500000000001</v>
       </c>
       <c r="G91">
         <v>30.7</v>
@@ -8749,28 +8749,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M91">
-        <v>61.69399900000001</v>
+        <v>62.38719000000001</v>
       </c>
       <c r="N91">
-        <v>81.23933433333333</v>
+        <v>80.54614333333333</v>
       </c>
       <c r="O91">
-        <v>24.3718003</v>
+        <v>24.163843</v>
       </c>
       <c r="P91">
-        <v>56.86753403333333</v>
+        <v>56.38230033333333</v>
       </c>
       <c r="Q91">
-        <v>57.76753403333332</v>
+        <v>57.28230033333332</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.320149964556233</v>
+        <v>0.3463498247457777</v>
       </c>
       <c r="T91">
-        <v>3.992126269558036</v>
+        <v>4.373366158874629</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.316810964601814</v>
+        <v>2.291068620550682</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08238898247457777</v>
+        <v>0.08233806884796993</v>
       </c>
       <c r="C92">
-        <v>72.68639951974001</v>
+        <v>64.21328834426549</v>
       </c>
       <c r="D92">
-        <v>865.03639951974</v>
+        <v>865.7082883442655</v>
       </c>
       <c r="E92">
-        <v>194.35</v>
+        <v>203.495</v>
       </c>
       <c r="F92">
-        <v>823.0500000000001</v>
+        <v>832.1950000000001</v>
       </c>
       <c r="G92">
         <v>30.7</v>
@@ -8831,28 +8831,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M92">
-        <v>62.38719000000001</v>
+        <v>63.08038100000001</v>
       </c>
       <c r="N92">
-        <v>80.54614333333333</v>
+        <v>79.85295233333332</v>
       </c>
       <c r="O92">
-        <v>24.163843</v>
+        <v>23.9558857</v>
       </c>
       <c r="P92">
-        <v>56.38230033333333</v>
+        <v>55.89706663333332</v>
       </c>
       <c r="Q92">
-        <v>57.28230033333332</v>
+        <v>56.79706663333332</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3463498247457777</v>
+        <v>0.3783718760885548</v>
       </c>
       <c r="T92">
-        <v>4.373366158874629</v>
+        <v>4.83932602359491</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.291068620550682</v>
+        <v>2.265892042302872</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08233806884796993</v>
+        <v>0.08228715522136207</v>
       </c>
       <c r="C93">
-        <v>64.21328834426549</v>
+        <v>55.74122171559293</v>
       </c>
       <c r="D93">
-        <v>865.7082883442655</v>
+        <v>866.3812217155929</v>
       </c>
       <c r="E93">
-        <v>203.495</v>
+        <v>212.64</v>
       </c>
       <c r="F93">
-        <v>832.1950000000001</v>
+        <v>841.34</v>
       </c>
       <c r="G93">
         <v>30.7</v>
@@ -8913,28 +8913,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M93">
-        <v>63.08038100000001</v>
+        <v>63.77357200000001</v>
       </c>
       <c r="N93">
-        <v>79.85295233333332</v>
+        <v>79.15976133333334</v>
       </c>
       <c r="O93">
-        <v>23.9558857</v>
+        <v>23.7479284</v>
       </c>
       <c r="P93">
-        <v>55.89706663333332</v>
+        <v>55.41183293333334</v>
       </c>
       <c r="Q93">
-        <v>56.79706663333332</v>
+        <v>56.31183293333333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3783718760885548</v>
+        <v>0.418399440267026</v>
       </c>
       <c r="T93">
-        <v>4.83932602359491</v>
+        <v>5.421775854495261</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.265892042302872</v>
+        <v>2.241262780973494</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08228715522136207</v>
+        <v>0.08223624159475421</v>
       </c>
       <c r="C94">
-        <v>55.74122171559293</v>
+        <v>47.27020207146188</v>
       </c>
       <c r="D94">
-        <v>866.3812217155929</v>
+        <v>867.0552020714618</v>
       </c>
       <c r="E94">
-        <v>212.64</v>
+        <v>221.785</v>
       </c>
       <c r="F94">
-        <v>841.34</v>
+        <v>850.485</v>
       </c>
       <c r="G94">
         <v>30.7</v>
@@ -8995,28 +8995,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M94">
-        <v>63.77357200000001</v>
+        <v>64.466763</v>
       </c>
       <c r="N94">
-        <v>79.15976133333334</v>
+        <v>78.46657033333334</v>
       </c>
       <c r="O94">
-        <v>23.7479284</v>
+        <v>23.5399711</v>
       </c>
       <c r="P94">
-        <v>55.41183293333334</v>
+        <v>54.92659923333333</v>
       </c>
       <c r="Q94">
-        <v>56.31183293333333</v>
+        <v>55.82659923333333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.418399440267026</v>
+        <v>0.4698634513536318</v>
       </c>
       <c r="T94">
-        <v>5.421775854495261</v>
+        <v>6.170639922795712</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.241262780973494</v>
+        <v>2.21716318117808</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08223624159475421</v>
+        <v>0.08218532796814637</v>
       </c>
       <c r="C95">
-        <v>47.27020207146188</v>
+        <v>38.80023185720313</v>
       </c>
       <c r="D95">
-        <v>867.0552020714618</v>
+        <v>867.7302318572032</v>
       </c>
       <c r="E95">
-        <v>221.785</v>
+        <v>230.9300000000001</v>
       </c>
       <c r="F95">
-        <v>850.485</v>
+        <v>859.6300000000001</v>
       </c>
       <c r="G95">
         <v>30.7</v>
@@ -9077,28 +9077,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M95">
-        <v>64.466763</v>
+        <v>65.15995400000001</v>
       </c>
       <c r="N95">
-        <v>78.46657033333334</v>
+        <v>77.77337933333332</v>
       </c>
       <c r="O95">
-        <v>23.5399711</v>
+        <v>23.3320138</v>
       </c>
       <c r="P95">
-        <v>54.92659923333333</v>
+        <v>54.44136553333333</v>
       </c>
       <c r="Q95">
-        <v>55.82659923333333</v>
+        <v>55.34136553333332</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4698634513536318</v>
+        <v>0.5384821328024397</v>
       </c>
       <c r="T95">
-        <v>6.170639922795712</v>
+        <v>7.169125347196315</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.21716318117808</v>
+        <v>2.193576338825121</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08218532796814637</v>
+        <v>0.08213441434153851</v>
       </c>
       <c r="C96">
-        <v>38.80023185720313</v>
+        <v>30.33131352577004</v>
       </c>
       <c r="D96">
-        <v>867.7302318572032</v>
+        <v>868.4063135257701</v>
       </c>
       <c r="E96">
-        <v>230.9300000000001</v>
+        <v>240.075</v>
       </c>
       <c r="F96">
-        <v>859.6300000000001</v>
+        <v>868.7750000000001</v>
       </c>
       <c r="G96">
         <v>30.7</v>
@@ -9159,28 +9159,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M96">
-        <v>65.15995400000001</v>
+        <v>65.85314500000001</v>
       </c>
       <c r="N96">
-        <v>77.77337933333332</v>
+        <v>77.08018833333333</v>
       </c>
       <c r="O96">
-        <v>23.3320138</v>
+        <v>23.1240565</v>
       </c>
       <c r="P96">
-        <v>54.44136553333333</v>
+        <v>53.95613183333333</v>
       </c>
       <c r="Q96">
-        <v>55.34136553333332</v>
+        <v>54.85613183333332</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5384821328024397</v>
+        <v>0.6345482868307708</v>
       </c>
       <c r="T96">
-        <v>7.169125347196315</v>
+        <v>8.56700494135716</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.193576338825121</v>
+        <v>2.17048606157433</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08213441434153851</v>
+        <v>0.08208350071493065</v>
       </c>
       <c r="C97">
-        <v>30.33131352577004</v>
+        <v>21.86344953776506</v>
       </c>
       <c r="D97">
-        <v>868.4063135257701</v>
+        <v>869.0834495377651</v>
       </c>
       <c r="E97">
-        <v>240.075</v>
+        <v>249.22</v>
       </c>
       <c r="F97">
-        <v>868.7750000000001</v>
+        <v>877.9200000000001</v>
       </c>
       <c r="G97">
         <v>30.7</v>
@@ -9241,28 +9241,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M97">
-        <v>65.85314500000001</v>
+        <v>66.54633600000001</v>
       </c>
       <c r="N97">
-        <v>77.08018833333333</v>
+        <v>76.38699733333333</v>
       </c>
       <c r="O97">
-        <v>23.1240565</v>
+        <v>22.9160992</v>
       </c>
       <c r="P97">
-        <v>53.95613183333333</v>
+        <v>53.47089813333333</v>
       </c>
       <c r="Q97">
-        <v>54.85613183333332</v>
+        <v>54.37089813333332</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6345482868307708</v>
+        <v>0.7786475178732676</v>
       </c>
       <c r="T97">
-        <v>8.56700494135716</v>
+        <v>10.66382433259843</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.17048606157433</v>
+        <v>2.147876831766265</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08208350071493065</v>
+        <v>0.0820325870883228</v>
       </c>
       <c r="C98">
-        <v>21.86344953776518</v>
+        <v>13.39664236147189</v>
       </c>
       <c r="D98">
-        <v>869.0834495377651</v>
+        <v>869.7616423614718</v>
       </c>
       <c r="E98">
-        <v>249.2199999999999</v>
+        <v>258.3649999999999</v>
       </c>
       <c r="F98">
-        <v>877.92</v>
+        <v>887.0649999999999</v>
       </c>
       <c r="G98">
         <v>30.7</v>
@@ -9323,28 +9323,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M98">
-        <v>66.546336</v>
+        <v>67.239527</v>
       </c>
       <c r="N98">
-        <v>76.38699733333334</v>
+        <v>75.69380633333334</v>
       </c>
       <c r="O98">
-        <v>22.9160992</v>
+        <v>22.7081419</v>
       </c>
       <c r="P98">
-        <v>53.47089813333334</v>
+        <v>52.98566443333334</v>
       </c>
       <c r="Q98">
-        <v>54.37089813333333</v>
+        <v>53.88566443333333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7786475178732655</v>
+        <v>1.018812902944092</v>
       </c>
       <c r="T98">
-        <v>10.6638243325984</v>
+        <v>14.1585233180005</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.147876831766265</v>
+        <v>2.125733771644963</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0820325870883228</v>
+        <v>0.08198167346171495</v>
       </c>
       <c r="C99">
-        <v>13.39664236147189</v>
+        <v>4.930894472884461</v>
       </c>
       <c r="D99">
-        <v>869.7616423614718</v>
+        <v>870.4408944728845</v>
       </c>
       <c r="E99">
-        <v>258.3649999999999</v>
+        <v>267.51</v>
       </c>
       <c r="F99">
-        <v>887.0649999999999</v>
+        <v>896.21</v>
       </c>
       <c r="G99">
         <v>30.7</v>
@@ -9405,28 +9405,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M99">
-        <v>67.239527</v>
+        <v>67.93271800000001</v>
       </c>
       <c r="N99">
-        <v>75.69380633333334</v>
+        <v>75.00061533333333</v>
       </c>
       <c r="O99">
-        <v>22.7081419</v>
+        <v>22.5001846</v>
       </c>
       <c r="P99">
-        <v>52.98566443333334</v>
+        <v>52.50043073333333</v>
       </c>
       <c r="Q99">
-        <v>53.88566443333333</v>
+        <v>53.40043073333332</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.018812902944092</v>
+        <v>1.499143673085746</v>
       </c>
       <c r="T99">
-        <v>14.1585233180005</v>
+        <v>21.14792128880469</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.125733771644963</v>
+        <v>2.10404261070981</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08198167346171495</v>
+        <v>0.08193075983510709</v>
       </c>
       <c r="C100">
-        <v>4.930894472884461</v>
+        <v>-3.533791644261782</v>
       </c>
       <c r="D100">
-        <v>870.4408944728845</v>
+        <v>871.1212083557382</v>
       </c>
       <c r="E100">
-        <v>267.51</v>
+        <v>276.655</v>
       </c>
       <c r="F100">
-        <v>896.21</v>
+        <v>905.355</v>
       </c>
       <c r="G100">
         <v>30.7</v>
@@ -9487,28 +9487,28 @@
         <v>142.9333333333333</v>
       </c>
       <c r="M100">
-        <v>67.93271800000001</v>
+        <v>68.62590900000001</v>
       </c>
       <c r="N100">
-        <v>75.00061533333333</v>
+        <v>74.30742433333333</v>
       </c>
       <c r="O100">
-        <v>22.5001846</v>
+        <v>22.2922273</v>
       </c>
       <c r="P100">
-        <v>52.50043073333333</v>
+        <v>52.01519703333334</v>
       </c>
       <c r="Q100">
-        <v>53.40043073333332</v>
+        <v>52.91519703333333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.499143673085746</v>
+        <v>2.940135983510706</v>
       </c>
       <c r="T100">
-        <v>21.14792128880469</v>
+        <v>42.11611520121728</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.10404261070981</v>
+        <v>2.082789655046075</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08193075983510709</v>
-      </c>
-      <c r="C101">
-        <v>-3.533791644261782</v>
-      </c>
-      <c r="D101">
-        <v>871.1212083557382</v>
-      </c>
-      <c r="E101">
-        <v>276.655</v>
-      </c>
-      <c r="F101">
-        <v>905.355</v>
-      </c>
-      <c r="G101">
-        <v>30.7</v>
-      </c>
-      <c r="H101">
-        <v>285.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>143.8333333333333</v>
-      </c>
-      <c r="K101">
-        <v>0.8999999999999915</v>
-      </c>
-      <c r="L101">
-        <v>142.9333333333333</v>
-      </c>
-      <c r="M101">
-        <v>68.62590900000001</v>
-      </c>
-      <c r="N101">
-        <v>74.30742433333333</v>
-      </c>
-      <c r="O101">
-        <v>22.2922273</v>
-      </c>
-      <c r="P101">
-        <v>52.01519703333334</v>
-      </c>
-      <c r="Q101">
-        <v>52.91519703333333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.940135983510706</v>
-      </c>
-      <c r="T101">
-        <v>42.11611520121728</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.05306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.082789655046075</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
